--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595906</v>
+        <v>122595590</v>
       </c>
       <c r="B2" t="n">
-        <v>79641</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800557</v>
+        <v>800672</v>
       </c>
       <c r="R2" t="n">
-        <v>7429273</v>
+        <v>7429603</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,19 +769,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595629</v>
+        <v>122595609</v>
       </c>
       <c r="B3" t="n">
         <v>98237</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800859</v>
+        <v>800532</v>
       </c>
       <c r="R3" t="n">
-        <v>7429527</v>
+        <v>7429301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595625</v>
+        <v>122595900</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>79274</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800705</v>
+        <v>800793</v>
       </c>
       <c r="R4" t="n">
-        <v>7429366</v>
+        <v>7429346</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,22 +981,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595913</v>
+        <v>122595635</v>
       </c>
       <c r="B5" t="n">
-        <v>79641</v>
+        <v>97197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,16 +1031,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800413</v>
+        <v>800874</v>
       </c>
       <c r="R5" t="n">
-        <v>7429375</v>
+        <v>7429248</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,25 +1085,26 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595598</v>
+        <v>122595607</v>
       </c>
       <c r="B6" t="n">
         <v>98237</v>
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800643</v>
+        <v>800565</v>
       </c>
       <c r="R6" t="n">
-        <v>7429444</v>
+        <v>7429285</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,19 +1198,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595594</v>
+        <v>122595621</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800577</v>
+        <v>800914</v>
       </c>
       <c r="R7" t="n">
-        <v>7429596</v>
+        <v>7429341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,22 +1304,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595610</v>
+        <v>122595899</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>78393</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800519</v>
+        <v>800751</v>
       </c>
       <c r="R8" t="n">
-        <v>7429306</v>
+        <v>7429412</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,19 +1410,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595613</v>
+        <v>122595600</v>
       </c>
       <c r="B9" t="n">
         <v>98237</v>
@@ -1461,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800646</v>
+        <v>800475</v>
       </c>
       <c r="R9" t="n">
-        <v>7429350</v>
+        <v>7429573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,19 +1516,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595596</v>
+        <v>122595633</v>
       </c>
       <c r="B10" t="n">
         <v>98237</v>
@@ -1567,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800535</v>
+        <v>800657</v>
       </c>
       <c r="R10" t="n">
-        <v>7429581</v>
+        <v>7429608</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,22 +1622,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595592</v>
+        <v>122595897</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800614</v>
+        <v>800590</v>
       </c>
       <c r="R11" t="n">
-        <v>7429556</v>
+        <v>7429518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,12 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1723,22 +1728,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595635</v>
+        <v>122595639</v>
       </c>
       <c r="B12" t="n">
-        <v>97197</v>
+        <v>92101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>149</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1773,20 +1778,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800874</v>
+        <v>800773</v>
       </c>
       <c r="R12" t="n">
-        <v>7429248</v>
+        <v>7429354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,26 +1828,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595627</v>
+        <v>122595624</v>
       </c>
       <c r="B13" t="n">
         <v>98237</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800851</v>
+        <v>800706</v>
       </c>
       <c r="R13" t="n">
-        <v>7429442</v>
+        <v>7429365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,19 +1940,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595604</v>
+        <v>122595599</v>
       </c>
       <c r="B14" t="n">
         <v>98237</v>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800482</v>
+        <v>800643</v>
       </c>
       <c r="R14" t="n">
-        <v>7429353</v>
+        <v>7429452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,19 +2046,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595597</v>
+        <v>122595601</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800611</v>
+        <v>800590</v>
       </c>
       <c r="R15" t="n">
-        <v>7429547</v>
+        <v>7429490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,19 +2152,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595593</v>
+        <v>122595627</v>
       </c>
       <c r="B16" t="n">
         <v>98237</v>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800567</v>
+        <v>800851</v>
       </c>
       <c r="R16" t="n">
-        <v>7429589</v>
+        <v>7429442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,22 +2258,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595893</v>
+        <v>122595640</v>
       </c>
       <c r="B17" t="n">
-        <v>95784</v>
+        <v>78393</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800464</v>
+        <v>800769</v>
       </c>
       <c r="R17" t="n">
-        <v>7429456</v>
+        <v>7429437</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2364,22 +2364,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595599</v>
+        <v>122595634</v>
       </c>
       <c r="B18" t="n">
-        <v>98237</v>
+        <v>98155</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800643</v>
+        <v>800580</v>
       </c>
       <c r="R18" t="n">
-        <v>7429452</v>
+        <v>7429643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,22 +2470,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595916</v>
+        <v>122595636</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>97197</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2520,16 +2520,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800420</v>
+        <v>800929</v>
       </c>
       <c r="R19" t="n">
-        <v>7429384</v>
+        <v>7429308</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2560,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2570,25 +2574,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595630</v>
+        <v>122595612</v>
       </c>
       <c r="B20" t="n">
         <v>98237</v>
@@ -2632,10 +2637,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800696</v>
+        <v>800658</v>
       </c>
       <c r="R20" t="n">
-        <v>7429504</v>
+        <v>7429352</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,22 +2687,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595614</v>
+        <v>122595906</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>79641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2711,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800650</v>
+        <v>800557</v>
       </c>
       <c r="R21" t="n">
-        <v>7429351</v>
+        <v>7429273</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,12 +2773,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,22 +2793,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595609</v>
+        <v>122595913</v>
       </c>
       <c r="B22" t="n">
-        <v>98237</v>
+        <v>79641</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2844,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800532</v>
+        <v>800413</v>
       </c>
       <c r="R22" t="n">
-        <v>7429301</v>
+        <v>7429375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,12 +2879,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,22 +2899,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595898</v>
+        <v>122595605</v>
       </c>
       <c r="B23" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2923,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2950,10 +2955,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800726</v>
+        <v>800481</v>
       </c>
       <c r="R23" t="n">
-        <v>7429460</v>
+        <v>7429318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,12 +2985,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3000,22 +3005,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595636</v>
+        <v>122595603</v>
       </c>
       <c r="B24" t="n">
-        <v>97197</v>
+        <v>98237</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3029,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3050,20 +3055,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800929</v>
+        <v>800492</v>
       </c>
       <c r="R24" t="n">
-        <v>7429308</v>
+        <v>7429368</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,26 +3105,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595615</v>
+        <v>122595623</v>
       </c>
       <c r="B25" t="n">
         <v>98237</v>
@@ -3167,10 +3167,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800705</v>
+        <v>800714</v>
       </c>
       <c r="R25" t="n">
-        <v>7429329</v>
+        <v>7429368</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,19 +3217,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595628</v>
+        <v>122595608</v>
       </c>
       <c r="B26" t="n">
         <v>98237</v>
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800709</v>
+        <v>800522</v>
       </c>
       <c r="R26" t="n">
-        <v>7429466</v>
+        <v>7429299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,22 +3323,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595595</v>
+        <v>122595905</v>
       </c>
       <c r="B27" t="n">
-        <v>98237</v>
+        <v>79274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,25 +3347,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800518</v>
+        <v>800662</v>
       </c>
       <c r="R27" t="n">
-        <v>7429600</v>
+        <v>7429278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3429,19 +3429,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595603</v>
+        <v>122595593</v>
       </c>
       <c r="B28" t="n">
         <v>98237</v>
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800492</v>
+        <v>800567</v>
       </c>
       <c r="R28" t="n">
-        <v>7429368</v>
+        <v>7429589</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3535,19 +3535,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595602</v>
+        <v>122595594</v>
       </c>
       <c r="B29" t="n">
         <v>98237</v>
@@ -3591,10 +3591,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800439</v>
+        <v>800577</v>
       </c>
       <c r="R29" t="n">
-        <v>7429345</v>
+        <v>7429596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3641,19 +3641,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595632</v>
+        <v>122595604</v>
       </c>
       <c r="B30" t="n">
         <v>98237</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800635</v>
+        <v>800482</v>
       </c>
       <c r="R30" t="n">
-        <v>7429538</v>
+        <v>7429353</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,19 +3747,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595590</v>
+        <v>122595606</v>
       </c>
       <c r="B31" t="n">
         <v>98237</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800672</v>
+        <v>800535</v>
       </c>
       <c r="R31" t="n">
-        <v>7429603</v>
+        <v>7429362</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3853,22 +3853,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595915</v>
+        <v>122595614</v>
       </c>
       <c r="B32" t="n">
-        <v>79737</v>
+        <v>98237</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3877,25 +3877,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800419</v>
+        <v>800650</v>
       </c>
       <c r="R32" t="n">
-        <v>7429379</v>
+        <v>7429351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3959,22 +3959,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595901</v>
+        <v>122595610</v>
       </c>
       <c r="B33" t="n">
-        <v>78301</v>
+        <v>98237</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3983,25 +3983,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800786</v>
+        <v>800519</v>
       </c>
       <c r="R33" t="n">
-        <v>7429304</v>
+        <v>7429306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,12 +4045,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4065,22 +4065,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595899</v>
+        <v>122595901</v>
       </c>
       <c r="B34" t="n">
-        <v>78393</v>
+        <v>78301</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,21 +4093,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800751</v>
+        <v>800786</v>
       </c>
       <c r="R34" t="n">
-        <v>7429412</v>
+        <v>7429304</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4171,22 +4171,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595639</v>
+        <v>122595921</v>
       </c>
       <c r="B35" t="n">
-        <v>92101</v>
+        <v>78656</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,25 +4195,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>149</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800773</v>
+        <v>800444</v>
       </c>
       <c r="R35" t="n">
-        <v>7429354</v>
+        <v>7429388</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,22 +4277,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595616</v>
+        <v>122595916</v>
       </c>
       <c r="B36" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4301,25 +4301,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800708</v>
+        <v>800420</v>
       </c>
       <c r="R36" t="n">
-        <v>7429313</v>
+        <v>7429384</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4383,19 +4383,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595623</v>
+        <v>122595618</v>
       </c>
       <c r="B37" t="n">
         <v>98237</v>
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800714</v>
+        <v>800702</v>
       </c>
       <c r="R37" t="n">
-        <v>7429368</v>
+        <v>7429367</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,22 +4489,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595900</v>
+        <v>122595622</v>
       </c>
       <c r="B38" t="n">
-        <v>79274</v>
+        <v>98237</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800793</v>
+        <v>800857</v>
       </c>
       <c r="R38" t="n">
-        <v>7429346</v>
+        <v>7429342</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,12 +4575,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4595,22 +4595,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595914</v>
+        <v>122595893</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
+        <v>95784</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800417</v>
+        <v>800464</v>
       </c>
       <c r="R39" t="n">
-        <v>7429377</v>
+        <v>7429456</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4701,19 +4701,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595611</v>
+        <v>122595615</v>
       </c>
       <c r="B40" t="n">
         <v>98237</v>
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800599</v>
+        <v>800705</v>
       </c>
       <c r="R40" t="n">
-        <v>7429383</v>
+        <v>7429329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4807,22 +4807,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595608</v>
+        <v>122595911</v>
       </c>
       <c r="B41" t="n">
-        <v>98237</v>
+        <v>94263</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800522</v>
+        <v>800419</v>
       </c>
       <c r="R41" t="n">
-        <v>7429299</v>
+        <v>7429341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,22 +4913,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595638</v>
+        <v>122595910</v>
       </c>
       <c r="B42" t="n">
-        <v>92113</v>
+        <v>79641</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4941,21 +4941,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800789</v>
+        <v>800412</v>
       </c>
       <c r="R42" t="n">
-        <v>7429366</v>
+        <v>7429327</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,12 +4999,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5019,19 +5019,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595612</v>
+        <v>122595619</v>
       </c>
       <c r="B43" t="n">
         <v>98237</v>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800658</v>
+        <v>800707</v>
       </c>
       <c r="R43" t="n">
-        <v>7429352</v>
+        <v>7429357</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5125,19 +5125,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595633</v>
+        <v>122595616</v>
       </c>
       <c r="B44" t="n">
         <v>98237</v>
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800657</v>
+        <v>800708</v>
       </c>
       <c r="R44" t="n">
-        <v>7429608</v>
+        <v>7429313</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5231,19 +5231,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595624</v>
+        <v>122595630</v>
       </c>
       <c r="B45" t="n">
         <v>98237</v>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800706</v>
+        <v>800696</v>
       </c>
       <c r="R45" t="n">
-        <v>7429365</v>
+        <v>7429504</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5337,19 +5337,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595617</v>
+        <v>122595596</v>
       </c>
       <c r="B46" t="n">
         <v>98237</v>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800705</v>
+        <v>800535</v>
       </c>
       <c r="R46" t="n">
-        <v>7429310</v>
+        <v>7429581</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,22 +5443,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595911</v>
+        <v>122595903</v>
       </c>
       <c r="B47" t="n">
-        <v>94263</v>
+        <v>78393</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5467,25 +5467,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2387</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800419</v>
+        <v>800756</v>
       </c>
       <c r="R47" t="n">
-        <v>7429341</v>
+        <v>7429284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5549,22 +5549,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595897</v>
+        <v>122595602</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5573,25 +5573,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800590</v>
+        <v>800439</v>
       </c>
       <c r="R48" t="n">
-        <v>7429518</v>
+        <v>7429345</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,12 +5635,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,19 +5655,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595619</v>
+        <v>122595629</v>
       </c>
       <c r="B49" t="n">
         <v>98237</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800707</v>
+        <v>800859</v>
       </c>
       <c r="R49" t="n">
-        <v>7429357</v>
+        <v>7429527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,22 +5761,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595917</v>
+        <v>122595597</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>98237</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,25 +5785,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800422</v>
+        <v>800611</v>
       </c>
       <c r="R50" t="n">
-        <v>7429390</v>
+        <v>7429547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5867,22 +5867,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595921</v>
+        <v>122595611</v>
       </c>
       <c r="B51" t="n">
-        <v>78656</v>
+        <v>98237</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5891,25 +5891,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800444</v>
+        <v>800599</v>
       </c>
       <c r="R51" t="n">
-        <v>7429388</v>
+        <v>7429383</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5953,12 +5953,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,19 +5973,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595605</v>
+        <v>122595625</v>
       </c>
       <c r="B52" t="n">
         <v>98237</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800481</v>
+        <v>800705</v>
       </c>
       <c r="R52" t="n">
-        <v>7429318</v>
+        <v>7429366</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6079,19 +6079,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595600</v>
+        <v>122595620</v>
       </c>
       <c r="B53" t="n">
         <v>98237</v>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800475</v>
+        <v>800882</v>
       </c>
       <c r="R53" t="n">
-        <v>7429573</v>
+        <v>7429337</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6185,19 +6185,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595620</v>
+        <v>122595595</v>
       </c>
       <c r="B54" t="n">
         <v>98237</v>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800882</v>
+        <v>800518</v>
       </c>
       <c r="R54" t="n">
-        <v>7429337</v>
+        <v>7429600</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6291,19 +6291,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595606</v>
+        <v>122595598</v>
       </c>
       <c r="B55" t="n">
         <v>98237</v>
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800535</v>
+        <v>800643</v>
       </c>
       <c r="R55" t="n">
-        <v>7429362</v>
+        <v>7429444</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6397,22 +6397,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595902</v>
+        <v>122595613</v>
       </c>
       <c r="B56" t="n">
-        <v>78393</v>
+        <v>98237</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6421,25 +6421,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800768</v>
+        <v>800646</v>
       </c>
       <c r="R56" t="n">
-        <v>7429299</v>
+        <v>7429350</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6483,12 +6483,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6503,19 +6503,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595618</v>
+        <v>122595628</v>
       </c>
       <c r="B57" t="n">
         <v>98237</v>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800702</v>
+        <v>800709</v>
       </c>
       <c r="R57" t="n">
-        <v>7429367</v>
+        <v>7429466</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,19 +6609,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595903</v>
+        <v>122595902</v>
       </c>
       <c r="B58" t="n">
         <v>78393</v>
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800756</v>
+        <v>800768</v>
       </c>
       <c r="R58" t="n">
-        <v>7429284</v>
+        <v>7429299</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6715,22 +6715,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595634</v>
+        <v>122595914</v>
       </c>
       <c r="B59" t="n">
-        <v>98155</v>
+        <v>79737</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6739,25 +6739,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>223591</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800580</v>
+        <v>800417</v>
       </c>
       <c r="R59" t="n">
-        <v>7429643</v>
+        <v>7429377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6821,22 +6821,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595591</v>
+        <v>122595915</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6845,25 +6845,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800604</v>
+        <v>800419</v>
       </c>
       <c r="R60" t="n">
-        <v>7429623</v>
+        <v>7429379</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6907,12 +6907,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6927,22 +6927,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595905</v>
+        <v>122595917</v>
       </c>
       <c r="B61" t="n">
-        <v>79274</v>
+        <v>79737</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6955,21 +6955,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800662</v>
+        <v>800422</v>
       </c>
       <c r="R61" t="n">
-        <v>7429278</v>
+        <v>7429390</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7033,19 +7033,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595607</v>
+        <v>122595592</v>
       </c>
       <c r="B62" t="n">
         <v>98237</v>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800565</v>
+        <v>800614</v>
       </c>
       <c r="R62" t="n">
-        <v>7429285</v>
+        <v>7429556</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7139,19 +7139,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595601</v>
+        <v>122595632</v>
       </c>
       <c r="B63" t="n">
         <v>98237</v>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800590</v>
+        <v>800635</v>
       </c>
       <c r="R63" t="n">
-        <v>7429490</v>
+        <v>7429538</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7245,22 +7245,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595640</v>
+        <v>122595898</v>
       </c>
       <c r="B64" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7273,21 +7273,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800769</v>
+        <v>800726</v>
       </c>
       <c r="R64" t="n">
-        <v>7429437</v>
+        <v>7429460</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7351,22 +7351,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595910</v>
+        <v>122595591</v>
       </c>
       <c r="B65" t="n">
-        <v>79641</v>
+        <v>98237</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7375,25 +7375,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800412</v>
+        <v>800604</v>
       </c>
       <c r="R65" t="n">
-        <v>7429327</v>
+        <v>7429623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7457,22 +7457,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595622</v>
+        <v>122595638</v>
       </c>
       <c r="B66" t="n">
-        <v>98237</v>
+        <v>92113</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800857</v>
+        <v>800789</v>
       </c>
       <c r="R66" t="n">
-        <v>7429342</v>
+        <v>7429366</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7563,19 +7563,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595621</v>
+        <v>122595617</v>
       </c>
       <c r="B67" t="n">
         <v>98237</v>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800914</v>
+        <v>800705</v>
       </c>
       <c r="R67" t="n">
-        <v>7429341</v>
+        <v>7429310</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,12 +7669,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén, Jan Apelqvist</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595636</v>
+        <v>122595612</v>
       </c>
       <c r="B19" t="n">
-        <v>97197</v>
+        <v>98237</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2520,20 +2520,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800929</v>
+        <v>800658</v>
       </c>
       <c r="R19" t="n">
-        <v>7429308</v>
+        <v>7429352</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2570,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2593,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595612</v>
+        <v>122595636</v>
       </c>
       <c r="B20" t="n">
-        <v>98237</v>
+        <v>97197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2631,16 +2626,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800658</v>
+        <v>800929</v>
       </c>
       <c r="R20" t="n">
-        <v>7429352</v>
+        <v>7429308</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,6 +2680,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4077,10 +4077,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595901</v>
+        <v>122595622</v>
       </c>
       <c r="B34" t="n">
-        <v>78301</v>
+        <v>98237</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4089,25 +4089,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800786</v>
+        <v>800857</v>
       </c>
       <c r="R34" t="n">
-        <v>7429304</v>
+        <v>7429342</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4289,10 +4289,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595916</v>
+        <v>122595901</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
+        <v>78301</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,21 +4305,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800420</v>
+        <v>800786</v>
       </c>
       <c r="R36" t="n">
-        <v>7429384</v>
+        <v>7429304</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595618</v>
+        <v>122595916</v>
       </c>
       <c r="B37" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,25 +4407,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4439,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800702</v>
+        <v>800420</v>
       </c>
       <c r="R37" t="n">
-        <v>7429367</v>
+        <v>7429384</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4501,7 +4501,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595622</v>
+        <v>122595618</v>
       </c>
       <c r="B38" t="n">
         <v>98237</v>
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800857</v>
+        <v>800702</v>
       </c>
       <c r="R38" t="n">
-        <v>7429342</v>
+        <v>7429367</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595893</v>
+        <v>122595615</v>
       </c>
       <c r="B39" t="n">
-        <v>95784</v>
+        <v>98237</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4619,25 +4619,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800464</v>
+        <v>800705</v>
       </c>
       <c r="R39" t="n">
-        <v>7429456</v>
+        <v>7429329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4713,10 +4713,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595615</v>
+        <v>122595893</v>
       </c>
       <c r="B40" t="n">
-        <v>98237</v>
+        <v>95784</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4725,25 +4725,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800705</v>
+        <v>800464</v>
       </c>
       <c r="R40" t="n">
-        <v>7429329</v>
+        <v>7429456</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4787,12 +4787,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4819,10 +4819,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595911</v>
+        <v>122595619</v>
       </c>
       <c r="B41" t="n">
-        <v>94263</v>
+        <v>98237</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4831,25 +4831,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800419</v>
+        <v>800707</v>
       </c>
       <c r="R41" t="n">
-        <v>7429341</v>
+        <v>7429357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4925,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595910</v>
+        <v>122595616</v>
       </c>
       <c r="B42" t="n">
-        <v>79641</v>
+        <v>98237</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4937,25 +4937,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800412</v>
+        <v>800708</v>
       </c>
       <c r="R42" t="n">
-        <v>7429327</v>
+        <v>7429313</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,12 +4999,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5031,10 +5031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595619</v>
+        <v>122595911</v>
       </c>
       <c r="B43" t="n">
-        <v>98237</v>
+        <v>94263</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,25 +5043,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800707</v>
+        <v>800419</v>
       </c>
       <c r="R43" t="n">
-        <v>7429357</v>
+        <v>7429341</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595616</v>
+        <v>122595910</v>
       </c>
       <c r="B44" t="n">
-        <v>98237</v>
+        <v>79641</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5149,25 +5149,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800708</v>
+        <v>800412</v>
       </c>
       <c r="R44" t="n">
-        <v>7429313</v>
+        <v>7429327</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,12 +5211,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5985,7 +5985,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595625</v>
+        <v>122595620</v>
       </c>
       <c r="B52" t="n">
         <v>98237</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800705</v>
+        <v>800882</v>
       </c>
       <c r="R52" t="n">
-        <v>7429366</v>
+        <v>7429337</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6091,7 +6091,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595620</v>
+        <v>122595625</v>
       </c>
       <c r="B53" t="n">
         <v>98237</v>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800882</v>
+        <v>800705</v>
       </c>
       <c r="R53" t="n">
-        <v>7429337</v>
+        <v>7429366</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595590</v>
+        <v>122595910</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>79641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800672</v>
+        <v>800412</v>
       </c>
       <c r="R2" t="n">
-        <v>7429603</v>
+        <v>7429327</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595609</v>
+        <v>122595915</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800532</v>
+        <v>800419</v>
       </c>
       <c r="R3" t="n">
-        <v>7429301</v>
+        <v>7429379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595900</v>
+        <v>122595639</v>
       </c>
       <c r="B4" t="n">
-        <v>79274</v>
+        <v>92102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>149</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800793</v>
+        <v>800773</v>
       </c>
       <c r="R4" t="n">
-        <v>7429346</v>
+        <v>7429354</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595635</v>
+        <v>122595594</v>
       </c>
       <c r="B5" t="n">
-        <v>97197</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1031,20 +1031,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800874</v>
+        <v>800577</v>
       </c>
       <c r="R5" t="n">
-        <v>7429248</v>
+        <v>7429596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1081,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1097,17 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595607</v>
+        <v>122595613</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800565</v>
+        <v>800646</v>
       </c>
       <c r="R6" t="n">
-        <v>7429285</v>
+        <v>7429350</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,17 +1198,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595621</v>
+        <v>122595617</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800914</v>
+        <v>800705</v>
       </c>
       <c r="R7" t="n">
-        <v>7429341</v>
+        <v>7429310</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,17 +1304,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595899</v>
+        <v>122595898</v>
       </c>
       <c r="B8" t="n">
-        <v>78393</v>
+        <v>78656</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1360,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800751</v>
+        <v>800726</v>
       </c>
       <c r="R8" t="n">
-        <v>7429412</v>
+        <v>7429460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595600</v>
+        <v>122595590</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800475</v>
+        <v>800672</v>
       </c>
       <c r="R9" t="n">
-        <v>7429573</v>
+        <v>7429603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,17 +1516,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595633</v>
+        <v>122595604</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1572,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800657</v>
+        <v>800482</v>
       </c>
       <c r="R10" t="n">
-        <v>7429608</v>
+        <v>7429353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,17 +1622,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595897</v>
+        <v>122595610</v>
       </c>
       <c r="B11" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1678,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800590</v>
+        <v>800519</v>
       </c>
       <c r="R11" t="n">
-        <v>7429518</v>
+        <v>7429306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,17 +1728,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595639</v>
+        <v>122595623</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1756,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1784,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800773</v>
+        <v>800714</v>
       </c>
       <c r="R12" t="n">
-        <v>7429354</v>
+        <v>7429368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,17 +1834,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595624</v>
+        <v>122595629</v>
       </c>
       <c r="B13" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800706</v>
+        <v>800859</v>
       </c>
       <c r="R13" t="n">
-        <v>7429365</v>
+        <v>7429527</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,17 +1940,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595599</v>
+        <v>122595621</v>
       </c>
       <c r="B14" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1996,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800643</v>
+        <v>800914</v>
       </c>
       <c r="R14" t="n">
-        <v>7429452</v>
+        <v>7429341</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,17 +2046,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595601</v>
+        <v>122595921</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,25 +2065,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2102,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800590</v>
+        <v>800444</v>
       </c>
       <c r="R15" t="n">
-        <v>7429490</v>
+        <v>7429388</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,12 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2164,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595627</v>
+        <v>122595598</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800851</v>
+        <v>800643</v>
       </c>
       <c r="R16" t="n">
-        <v>7429442</v>
+        <v>7429444</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,17 +2258,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595640</v>
+        <v>122595620</v>
       </c>
       <c r="B17" t="n">
-        <v>78393</v>
+        <v>98240</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2282,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2314,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800769</v>
+        <v>800882</v>
       </c>
       <c r="R17" t="n">
-        <v>7429437</v>
+        <v>7429337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,17 +2364,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595634</v>
+        <v>122595622</v>
       </c>
       <c r="B18" t="n">
-        <v>98155</v>
+        <v>98240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800580</v>
+        <v>800857</v>
       </c>
       <c r="R18" t="n">
-        <v>7429643</v>
+        <v>7429342</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,17 +2470,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595612</v>
+        <v>122595905</v>
       </c>
       <c r="B19" t="n">
-        <v>98237</v>
+        <v>79274</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2526,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800658</v>
+        <v>800662</v>
       </c>
       <c r="R19" t="n">
-        <v>7429352</v>
+        <v>7429278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2551,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595636</v>
+        <v>122595893</v>
       </c>
       <c r="B20" t="n">
-        <v>97197</v>
+        <v>95786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2626,20 +2621,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800929</v>
+        <v>800464</v>
       </c>
       <c r="R20" t="n">
-        <v>7429308</v>
+        <v>7429456</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,12 +2657,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2680,7 +2671,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595906</v>
+        <v>122595636</v>
       </c>
       <c r="B21" t="n">
-        <v>79641</v>
+        <v>97200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2737,16 +2727,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800557</v>
+        <v>800929</v>
       </c>
       <c r="R21" t="n">
-        <v>7429273</v>
+        <v>7429308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,12 +2767,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2787,6 +2781,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2798,17 +2793,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595913</v>
+        <v>122595628</v>
       </c>
       <c r="B22" t="n">
-        <v>79641</v>
+        <v>98240</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800413</v>
+        <v>800709</v>
       </c>
       <c r="R22" t="n">
-        <v>7429375</v>
+        <v>7429466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,12 +2874,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,17 +2899,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595605</v>
+        <v>122595592</v>
       </c>
       <c r="B23" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2955,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800481</v>
+        <v>800614</v>
       </c>
       <c r="R23" t="n">
-        <v>7429318</v>
+        <v>7429556</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3010,17 +3005,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595603</v>
+        <v>122595916</v>
       </c>
       <c r="B24" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3061,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800492</v>
+        <v>800420</v>
       </c>
       <c r="R24" t="n">
-        <v>7429368</v>
+        <v>7429384</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,12 +3086,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595623</v>
+        <v>122595632</v>
       </c>
       <c r="B25" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800714</v>
+        <v>800635</v>
       </c>
       <c r="R25" t="n">
-        <v>7429368</v>
+        <v>7429538</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,17 +3217,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595608</v>
+        <v>122595914</v>
       </c>
       <c r="B26" t="n">
-        <v>98237</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3273,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800522</v>
+        <v>800417</v>
       </c>
       <c r="R26" t="n">
-        <v>7429299</v>
+        <v>7429377</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,12 +3298,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595905</v>
+        <v>122595618</v>
       </c>
       <c r="B27" t="n">
-        <v>79274</v>
+        <v>98240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3347,25 +3342,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3379,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800662</v>
+        <v>800702</v>
       </c>
       <c r="R27" t="n">
-        <v>7429278</v>
+        <v>7429367</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3409,12 +3404,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,17 +3429,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595593</v>
+        <v>122595627</v>
       </c>
       <c r="B28" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3485,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800567</v>
+        <v>800851</v>
       </c>
       <c r="R28" t="n">
-        <v>7429589</v>
+        <v>7429442</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,17 +3535,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595594</v>
+        <v>122595901</v>
       </c>
       <c r="B29" t="n">
-        <v>98237</v>
+        <v>78301</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3559,25 +3554,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3591,10 +3586,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800577</v>
+        <v>800786</v>
       </c>
       <c r="R29" t="n">
-        <v>7429596</v>
+        <v>7429304</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,12 +3616,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3653,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595604</v>
+        <v>122595903</v>
       </c>
       <c r="B30" t="n">
-        <v>98237</v>
+        <v>78393</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3665,25 +3660,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3697,10 +3692,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800482</v>
+        <v>800756</v>
       </c>
       <c r="R30" t="n">
-        <v>7429353</v>
+        <v>7429284</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3727,12 +3722,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3759,10 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595606</v>
+        <v>122595897</v>
       </c>
       <c r="B31" t="n">
-        <v>98237</v>
+        <v>78656</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,25 +3766,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3803,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800535</v>
+        <v>800590</v>
       </c>
       <c r="R31" t="n">
-        <v>7429362</v>
+        <v>7429518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3833,12 +3828,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3865,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595614</v>
+        <v>122595609</v>
       </c>
       <c r="B32" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,10 +3904,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800650</v>
+        <v>800532</v>
       </c>
       <c r="R32" t="n">
-        <v>7429351</v>
+        <v>7429301</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,17 +3959,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595610</v>
+        <v>122595616</v>
       </c>
       <c r="B33" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4015,10 +4010,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800519</v>
+        <v>800708</v>
       </c>
       <c r="R33" t="n">
-        <v>7429306</v>
+        <v>7429313</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,17 +4065,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595622</v>
+        <v>122595597</v>
       </c>
       <c r="B34" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4121,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800857</v>
+        <v>800611</v>
       </c>
       <c r="R34" t="n">
-        <v>7429342</v>
+        <v>7429547</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,17 +4171,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595921</v>
+        <v>122595602</v>
       </c>
       <c r="B35" t="n">
-        <v>78656</v>
+        <v>98240</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,25 +4190,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4227,10 +4222,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800444</v>
+        <v>800439</v>
       </c>
       <c r="R35" t="n">
-        <v>7429388</v>
+        <v>7429345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,12 +4252,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4282,17 +4277,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595901</v>
+        <v>122595899</v>
       </c>
       <c r="B36" t="n">
-        <v>78301</v>
+        <v>78393</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4305,21 +4300,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800786</v>
+        <v>800751</v>
       </c>
       <c r="R36" t="n">
-        <v>7429304</v>
+        <v>7429412</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4395,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595916</v>
+        <v>122595630</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4407,25 +4402,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4439,10 +4434,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800420</v>
+        <v>800696</v>
       </c>
       <c r="R37" t="n">
-        <v>7429384</v>
+        <v>7429504</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,12 +4464,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,17 +4489,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595618</v>
+        <v>122595595</v>
       </c>
       <c r="B38" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4545,10 +4540,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800702</v>
+        <v>800518</v>
       </c>
       <c r="R38" t="n">
-        <v>7429367</v>
+        <v>7429600</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4600,17 +4595,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595615</v>
+        <v>122595619</v>
       </c>
       <c r="B39" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4651,10 +4646,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800705</v>
+        <v>800707</v>
       </c>
       <c r="R39" t="n">
-        <v>7429329</v>
+        <v>7429357</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4706,17 +4701,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595893</v>
+        <v>122595917</v>
       </c>
       <c r="B40" t="n">
-        <v>95784</v>
+        <v>79737</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,21 +4724,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4757,10 +4752,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800464</v>
+        <v>800422</v>
       </c>
       <c r="R40" t="n">
-        <v>7429456</v>
+        <v>7429390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,10 +4814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595619</v>
+        <v>122595593</v>
       </c>
       <c r="B41" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4863,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800707</v>
+        <v>800567</v>
       </c>
       <c r="R41" t="n">
-        <v>7429357</v>
+        <v>7429589</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4918,17 +4913,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595616</v>
+        <v>122595635</v>
       </c>
       <c r="B42" t="n">
-        <v>98237</v>
+        <v>97200</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4937,25 +4932,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4963,16 +4958,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800708</v>
+        <v>800874</v>
       </c>
       <c r="R42" t="n">
-        <v>7429313</v>
+        <v>7429248</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5013,6 +5012,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5024,17 +5024,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595911</v>
+        <v>122595624</v>
       </c>
       <c r="B43" t="n">
-        <v>94263</v>
+        <v>98240</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5043,25 +5043,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800419</v>
+        <v>800706</v>
       </c>
       <c r="R43" t="n">
-        <v>7429341</v>
+        <v>7429365</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5130,17 +5130,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595910</v>
+        <v>122595607</v>
       </c>
       <c r="B44" t="n">
-        <v>79641</v>
+        <v>98240</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5149,25 +5149,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800412</v>
+        <v>800565</v>
       </c>
       <c r="R44" t="n">
-        <v>7429327</v>
+        <v>7429285</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,12 +5211,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5236,17 +5236,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595630</v>
+        <v>122595615</v>
       </c>
       <c r="B45" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800696</v>
+        <v>800705</v>
       </c>
       <c r="R45" t="n">
-        <v>7429504</v>
+        <v>7429329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595596</v>
+        <v>122595906</v>
       </c>
       <c r="B46" t="n">
-        <v>98237</v>
+        <v>79641</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5361,25 +5361,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800535</v>
+        <v>800557</v>
       </c>
       <c r="R46" t="n">
-        <v>7429581</v>
+        <v>7429273</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5455,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595903</v>
+        <v>122595913</v>
       </c>
       <c r="B47" t="n">
-        <v>78393</v>
+        <v>79641</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5467,25 +5467,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800756</v>
+        <v>800413</v>
       </c>
       <c r="R47" t="n">
-        <v>7429284</v>
+        <v>7429375</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,10 +5561,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595602</v>
+        <v>122595600</v>
       </c>
       <c r="B48" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800439</v>
+        <v>800475</v>
       </c>
       <c r="R48" t="n">
-        <v>7429345</v>
+        <v>7429573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5660,17 +5660,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595629</v>
+        <v>122595599</v>
       </c>
       <c r="B49" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800859</v>
+        <v>800643</v>
       </c>
       <c r="R49" t="n">
-        <v>7429527</v>
+        <v>7429452</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595597</v>
+        <v>122595596</v>
       </c>
       <c r="B50" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800611</v>
+        <v>800535</v>
       </c>
       <c r="R50" t="n">
-        <v>7429547</v>
+        <v>7429581</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5872,17 +5872,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595611</v>
+        <v>122595625</v>
       </c>
       <c r="B51" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800599</v>
+        <v>800705</v>
       </c>
       <c r="R51" t="n">
-        <v>7429383</v>
+        <v>7429366</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5978,17 +5978,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595620</v>
+        <v>122595633</v>
       </c>
       <c r="B52" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800882</v>
+        <v>800657</v>
       </c>
       <c r="R52" t="n">
-        <v>7429337</v>
+        <v>7429608</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6084,17 +6084,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595625</v>
+        <v>122595614</v>
       </c>
       <c r="B53" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800705</v>
+        <v>800650</v>
       </c>
       <c r="R53" t="n">
-        <v>7429366</v>
+        <v>7429351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6190,17 +6190,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595595</v>
+        <v>122595591</v>
       </c>
       <c r="B54" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800518</v>
+        <v>800604</v>
       </c>
       <c r="R54" t="n">
-        <v>7429600</v>
+        <v>7429623</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6296,17 +6296,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595598</v>
+        <v>122595640</v>
       </c>
       <c r="B55" t="n">
-        <v>98237</v>
+        <v>78393</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6315,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800643</v>
+        <v>800769</v>
       </c>
       <c r="R55" t="n">
-        <v>7429444</v>
+        <v>7429437</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6409,10 +6409,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595613</v>
+        <v>122595612</v>
       </c>
       <c r="B56" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800646</v>
+        <v>800658</v>
       </c>
       <c r="R56" t="n">
-        <v>7429350</v>
+        <v>7429352</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6508,17 +6508,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595628</v>
+        <v>122595608</v>
       </c>
       <c r="B57" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800709</v>
+        <v>800522</v>
       </c>
       <c r="R57" t="n">
-        <v>7429466</v>
+        <v>7429299</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,17 +6614,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595902</v>
+        <v>122595603</v>
       </c>
       <c r="B58" t="n">
-        <v>78393</v>
+        <v>98240</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6633,25 +6633,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800768</v>
+        <v>800492</v>
       </c>
       <c r="R58" t="n">
-        <v>7429299</v>
+        <v>7429368</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6695,12 +6695,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6720,17 +6720,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595914</v>
+        <v>122595606</v>
       </c>
       <c r="B59" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6739,25 +6739,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800417</v>
+        <v>800535</v>
       </c>
       <c r="R59" t="n">
-        <v>7429377</v>
+        <v>7429362</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6826,17 +6826,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595915</v>
+        <v>122595601</v>
       </c>
       <c r="B60" t="n">
-        <v>79737</v>
+        <v>98240</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6845,25 +6845,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800419</v>
+        <v>800590</v>
       </c>
       <c r="R60" t="n">
-        <v>7429379</v>
+        <v>7429490</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6907,12 +6907,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6932,17 +6932,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595917</v>
+        <v>122595900</v>
       </c>
       <c r="B61" t="n">
-        <v>79737</v>
+        <v>79274</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6955,21 +6955,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800422</v>
+        <v>800793</v>
       </c>
       <c r="R61" t="n">
-        <v>7429390</v>
+        <v>7429346</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595592</v>
+        <v>122595911</v>
       </c>
       <c r="B62" t="n">
-        <v>98237</v>
+        <v>94265</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7057,25 +7057,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800614</v>
+        <v>800419</v>
       </c>
       <c r="R62" t="n">
-        <v>7429556</v>
+        <v>7429341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7119,12 +7119,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7151,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595632</v>
+        <v>122595638</v>
       </c>
       <c r="B63" t="n">
-        <v>98237</v>
+        <v>92114</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7163,25 +7163,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800635</v>
+        <v>800789</v>
       </c>
       <c r="R63" t="n">
-        <v>7429538</v>
+        <v>7429366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595898</v>
+        <v>122595634</v>
       </c>
       <c r="B64" t="n">
-        <v>78656</v>
+        <v>98158</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7269,25 +7269,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>223591</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800726</v>
+        <v>800580</v>
       </c>
       <c r="R64" t="n">
-        <v>7429460</v>
+        <v>7429643</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7356,17 +7356,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595591</v>
+        <v>122595605</v>
       </c>
       <c r="B65" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800604</v>
+        <v>800481</v>
       </c>
       <c r="R65" t="n">
-        <v>7429623</v>
+        <v>7429318</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7462,17 +7462,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595638</v>
+        <v>122595902</v>
       </c>
       <c r="B66" t="n">
-        <v>92113</v>
+        <v>78393</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800789</v>
+        <v>800768</v>
       </c>
       <c r="R66" t="n">
-        <v>7429366</v>
+        <v>7429299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7543,12 +7543,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7575,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595617</v>
+        <v>122595611</v>
       </c>
       <c r="B67" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800705</v>
+        <v>800599</v>
       </c>
       <c r="R67" t="n">
-        <v>7429310</v>
+        <v>7429383</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595917</v>
+        <v>122595600</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,25 +3761,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800422</v>
+        <v>800475</v>
       </c>
       <c r="R31" t="n">
-        <v>7429390</v>
+        <v>7429573</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595600</v>
+        <v>122595917</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>79843</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3867,25 +3867,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800475</v>
+        <v>800422</v>
       </c>
       <c r="R32" t="n">
-        <v>7429573</v>
+        <v>7429390</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595604</v>
+        <v>122595603</v>
       </c>
       <c r="B39" t="n">
         <v>98347</v>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800482</v>
+        <v>800492</v>
       </c>
       <c r="R39" t="n">
-        <v>7429353</v>
+        <v>7429368</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595603</v>
+        <v>122595632</v>
       </c>
       <c r="B40" t="n">
         <v>98347</v>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800492</v>
+        <v>800635</v>
       </c>
       <c r="R40" t="n">
-        <v>7429368</v>
+        <v>7429538</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595632</v>
+        <v>122595601</v>
       </c>
       <c r="B41" t="n">
         <v>98347</v>
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800635</v>
+        <v>800590</v>
       </c>
       <c r="R41" t="n">
-        <v>7429538</v>
+        <v>7429490</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595601</v>
+        <v>122595604</v>
       </c>
       <c r="B42" t="n">
         <v>98347</v>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800590</v>
+        <v>800482</v>
       </c>
       <c r="R42" t="n">
-        <v>7429490</v>
+        <v>7429353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595600</v>
+        <v>122595917</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>79843</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,25 +3761,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800475</v>
+        <v>800422</v>
       </c>
       <c r="R31" t="n">
-        <v>7429573</v>
+        <v>7429390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595917</v>
+        <v>122595600</v>
       </c>
       <c r="B32" t="n">
-        <v>79843</v>
+        <v>98347</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3867,25 +3867,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800422</v>
+        <v>800475</v>
       </c>
       <c r="R32" t="n">
-        <v>7429390</v>
+        <v>7429573</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595610</v>
+        <v>122595599</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800519</v>
+        <v>800643</v>
       </c>
       <c r="R2" t="n">
-        <v>7429306</v>
+        <v>7429452</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595594</v>
+        <v>122595629</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800577</v>
+        <v>800859</v>
       </c>
       <c r="R3" t="n">
-        <v>7429596</v>
+        <v>7429527</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595614</v>
+        <v>122595602</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800650</v>
+        <v>800439</v>
       </c>
       <c r="R4" t="n">
-        <v>7429351</v>
+        <v>7429345</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595638</v>
+        <v>122595606</v>
       </c>
       <c r="B5" t="n">
-        <v>92221</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800789</v>
+        <v>800535</v>
       </c>
       <c r="R5" t="n">
-        <v>7429366</v>
+        <v>7429362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595620</v>
+        <v>122595598</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800882</v>
+        <v>800643</v>
       </c>
       <c r="R6" t="n">
-        <v>7429337</v>
+        <v>7429444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595623</v>
+        <v>122595604</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800714</v>
+        <v>800482</v>
       </c>
       <c r="R7" t="n">
-        <v>7429368</v>
+        <v>7429353</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595602</v>
+        <v>122595591</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800439</v>
+        <v>800604</v>
       </c>
       <c r="R8" t="n">
-        <v>7429345</v>
+        <v>7429623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595596</v>
+        <v>122595609</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800535</v>
+        <v>800532</v>
       </c>
       <c r="R9" t="n">
-        <v>7429581</v>
+        <v>7429301</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595921</v>
+        <v>122595893</v>
       </c>
       <c r="B10" t="n">
-        <v>78762</v>
+        <v>95901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800444</v>
+        <v>800464</v>
       </c>
       <c r="R10" t="n">
-        <v>7429388</v>
+        <v>7429456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595639</v>
+        <v>122595906</v>
       </c>
       <c r="B11" t="n">
-        <v>92209</v>
+        <v>79751</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>149</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800773</v>
+        <v>800557</v>
       </c>
       <c r="R11" t="n">
-        <v>7429354</v>
+        <v>7429273</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595624</v>
+        <v>122595623</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800706</v>
+        <v>800714</v>
       </c>
       <c r="R12" t="n">
-        <v>7429365</v>
+        <v>7429368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595606</v>
+        <v>122595613</v>
       </c>
       <c r="B13" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800535</v>
+        <v>800646</v>
       </c>
       <c r="R13" t="n">
-        <v>7429362</v>
+        <v>7429350</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595612</v>
+        <v>122595622</v>
       </c>
       <c r="B14" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800658</v>
+        <v>800857</v>
       </c>
       <c r="R14" t="n">
-        <v>7429352</v>
+        <v>7429342</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595629</v>
+        <v>122595612</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800859</v>
+        <v>800658</v>
       </c>
       <c r="R15" t="n">
-        <v>7429527</v>
+        <v>7429352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595608</v>
+        <v>122595625</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800522</v>
+        <v>800705</v>
       </c>
       <c r="R16" t="n">
-        <v>7429299</v>
+        <v>7429366</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595906</v>
+        <v>122595903</v>
       </c>
       <c r="B17" t="n">
-        <v>79747</v>
+        <v>78503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800557</v>
+        <v>800756</v>
       </c>
       <c r="R17" t="n">
-        <v>7429273</v>
+        <v>7429284</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595613</v>
+        <v>122595910</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>79751</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800646</v>
+        <v>800412</v>
       </c>
       <c r="R18" t="n">
-        <v>7429350</v>
+        <v>7429327</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595902</v>
+        <v>122595620</v>
       </c>
       <c r="B19" t="n">
-        <v>78499</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800768</v>
+        <v>800882</v>
       </c>
       <c r="R19" t="n">
-        <v>7429299</v>
+        <v>7429337</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595598</v>
+        <v>122595614</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800643</v>
+        <v>800650</v>
       </c>
       <c r="R20" t="n">
-        <v>7429444</v>
+        <v>7429351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595591</v>
+        <v>122595914</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800604</v>
+        <v>800417</v>
       </c>
       <c r="R21" t="n">
-        <v>7429623</v>
+        <v>7429377</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595915</v>
+        <v>122595921</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,21 +2811,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800419</v>
+        <v>800444</v>
       </c>
       <c r="R22" t="n">
-        <v>7429379</v>
+        <v>7429388</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595901</v>
+        <v>122595605</v>
       </c>
       <c r="B23" t="n">
-        <v>78407</v>
+        <v>98355</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800786</v>
+        <v>800481</v>
       </c>
       <c r="R23" t="n">
-        <v>7429304</v>
+        <v>7429318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595905</v>
+        <v>122595899</v>
       </c>
       <c r="B24" t="n">
-        <v>79380</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,21 +3023,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800662</v>
+        <v>800751</v>
       </c>
       <c r="R24" t="n">
-        <v>7429278</v>
+        <v>7429412</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595898</v>
+        <v>122595902</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800726</v>
+        <v>800768</v>
       </c>
       <c r="R25" t="n">
-        <v>7429460</v>
+        <v>7429299</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595597</v>
+        <v>122595630</v>
       </c>
       <c r="B26" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800611</v>
+        <v>800696</v>
       </c>
       <c r="R26" t="n">
-        <v>7429547</v>
+        <v>7429504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595617</v>
+        <v>122595633</v>
       </c>
       <c r="B27" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800705</v>
+        <v>800657</v>
       </c>
       <c r="R27" t="n">
-        <v>7429310</v>
+        <v>7429608</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595911</v>
+        <v>122595915</v>
       </c>
       <c r="B28" t="n">
-        <v>94372</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3478,7 +3478,7 @@
         <v>800419</v>
       </c>
       <c r="R28" t="n">
-        <v>7429341</v>
+        <v>7429379</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595605</v>
+        <v>122595897</v>
       </c>
       <c r="B29" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800481</v>
+        <v>800590</v>
       </c>
       <c r="R29" t="n">
-        <v>7429318</v>
+        <v>7429518</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595897</v>
+        <v>122595596</v>
       </c>
       <c r="B30" t="n">
-        <v>78762</v>
+        <v>98355</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,25 +3655,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800590</v>
+        <v>800535</v>
       </c>
       <c r="R30" t="n">
-        <v>7429518</v>
+        <v>7429581</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3749,10 +3749,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595917</v>
+        <v>122595628</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,25 +3761,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800422</v>
+        <v>800709</v>
       </c>
       <c r="R31" t="n">
-        <v>7429390</v>
+        <v>7429466</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595600</v>
+        <v>122595610</v>
       </c>
       <c r="B32" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800475</v>
+        <v>800519</v>
       </c>
       <c r="R32" t="n">
-        <v>7429573</v>
+        <v>7429306</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595900</v>
+        <v>122595624</v>
       </c>
       <c r="B33" t="n">
-        <v>79380</v>
+        <v>98355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,25 +3973,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800793</v>
+        <v>800706</v>
       </c>
       <c r="R33" t="n">
-        <v>7429346</v>
+        <v>7429365</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595609</v>
+        <v>122595618</v>
       </c>
       <c r="B34" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800532</v>
+        <v>800702</v>
       </c>
       <c r="R34" t="n">
-        <v>7429301</v>
+        <v>7429367</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595630</v>
+        <v>122595615</v>
       </c>
       <c r="B35" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800696</v>
+        <v>800705</v>
       </c>
       <c r="R35" t="n">
-        <v>7429504</v>
+        <v>7429329</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595633</v>
+        <v>122595638</v>
       </c>
       <c r="B36" t="n">
-        <v>98347</v>
+        <v>92225</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,25 +4291,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800657</v>
+        <v>800789</v>
       </c>
       <c r="R36" t="n">
-        <v>7429608</v>
+        <v>7429366</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,10 +4385,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595618</v>
+        <v>122595603</v>
       </c>
       <c r="B37" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800702</v>
+        <v>800492</v>
       </c>
       <c r="R37" t="n">
-        <v>7429367</v>
+        <v>7429368</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595903</v>
+        <v>122595600</v>
       </c>
       <c r="B38" t="n">
-        <v>78499</v>
+        <v>98355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4503,25 +4503,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800756</v>
+        <v>800475</v>
       </c>
       <c r="R38" t="n">
-        <v>7429284</v>
+        <v>7429573</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595603</v>
+        <v>122595592</v>
       </c>
       <c r="B39" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800492</v>
+        <v>800614</v>
       </c>
       <c r="R39" t="n">
-        <v>7429368</v>
+        <v>7429556</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595632</v>
+        <v>122595636</v>
       </c>
       <c r="B40" t="n">
-        <v>98347</v>
+        <v>97315</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4715,25 +4715,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4741,16 +4741,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800635</v>
+        <v>800929</v>
       </c>
       <c r="R40" t="n">
-        <v>7429538</v>
+        <v>7429308</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4791,6 +4795,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4809,10 +4814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595601</v>
+        <v>122595640</v>
       </c>
       <c r="B41" t="n">
-        <v>98347</v>
+        <v>78503</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,25 +4826,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800590</v>
+        <v>800769</v>
       </c>
       <c r="R41" t="n">
-        <v>7429490</v>
+        <v>7429437</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4915,10 +4920,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595604</v>
+        <v>122595905</v>
       </c>
       <c r="B42" t="n">
-        <v>98347</v>
+        <v>79384</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4927,25 +4932,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4959,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800482</v>
+        <v>800662</v>
       </c>
       <c r="R42" t="n">
-        <v>7429353</v>
+        <v>7429278</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,12 +4994,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5021,10 +5026,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595910</v>
+        <v>122595594</v>
       </c>
       <c r="B43" t="n">
-        <v>79747</v>
+        <v>98355</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5033,25 +5038,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800412</v>
+        <v>800577</v>
       </c>
       <c r="R43" t="n">
-        <v>7429327</v>
+        <v>7429596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5095,12 +5100,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5127,10 +5132,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595622</v>
+        <v>122595617</v>
       </c>
       <c r="B44" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5171,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800857</v>
+        <v>800705</v>
       </c>
       <c r="R44" t="n">
-        <v>7429342</v>
+        <v>7429310</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5233,10 +5238,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595607</v>
+        <v>122595597</v>
       </c>
       <c r="B45" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5277,10 +5282,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800565</v>
+        <v>800611</v>
       </c>
       <c r="R45" t="n">
-        <v>7429285</v>
+        <v>7429547</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5339,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595621</v>
+        <v>122595590</v>
       </c>
       <c r="B46" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800914</v>
+        <v>800672</v>
       </c>
       <c r="R46" t="n">
-        <v>7429341</v>
+        <v>7429603</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5445,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595635</v>
+        <v>122595627</v>
       </c>
       <c r="B47" t="n">
-        <v>97307</v>
+        <v>98355</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5457,25 +5462,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5483,20 +5488,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800874</v>
+        <v>800851</v>
       </c>
       <c r="R47" t="n">
-        <v>7429248</v>
+        <v>7429442</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5537,7 +5538,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5556,10 +5556,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595619</v>
+        <v>122595621</v>
       </c>
       <c r="B48" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800707</v>
+        <v>800914</v>
       </c>
       <c r="R48" t="n">
-        <v>7429357</v>
+        <v>7429341</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,10 +5662,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595611</v>
+        <v>122595608</v>
       </c>
       <c r="B49" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5706,10 +5706,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800599</v>
+        <v>800522</v>
       </c>
       <c r="R49" t="n">
-        <v>7429383</v>
+        <v>7429299</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595625</v>
+        <v>122595635</v>
       </c>
       <c r="B50" t="n">
-        <v>98347</v>
+        <v>97315</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5780,25 +5780,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5806,16 +5806,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800705</v>
+        <v>800874</v>
       </c>
       <c r="R50" t="n">
-        <v>7429366</v>
+        <v>7429248</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5856,6 +5860,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5874,10 +5879,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595893</v>
+        <v>122595619</v>
       </c>
       <c r="B51" t="n">
-        <v>95893</v>
+        <v>98355</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5886,25 +5891,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5918,10 +5923,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800464</v>
+        <v>800707</v>
       </c>
       <c r="R51" t="n">
-        <v>7429456</v>
+        <v>7429357</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5948,12 +5953,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5980,10 +5985,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595590</v>
+        <v>122595901</v>
       </c>
       <c r="B52" t="n">
-        <v>98347</v>
+        <v>78411</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5992,25 +5997,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6024,10 +6029,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800672</v>
+        <v>800786</v>
       </c>
       <c r="R52" t="n">
-        <v>7429603</v>
+        <v>7429304</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6059,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,10 +6091,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595616</v>
+        <v>122595898</v>
       </c>
       <c r="B53" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,25 +6103,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800708</v>
+        <v>800726</v>
       </c>
       <c r="R53" t="n">
-        <v>7429313</v>
+        <v>7429460</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,12 +6165,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6192,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595628</v>
+        <v>122595917</v>
       </c>
       <c r="B54" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6204,25 +6209,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6236,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800709</v>
+        <v>800422</v>
       </c>
       <c r="R54" t="n">
-        <v>7429466</v>
+        <v>7429390</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6266,12 +6271,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6298,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595916</v>
+        <v>122595595</v>
       </c>
       <c r="B55" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800420</v>
+        <v>800518</v>
       </c>
       <c r="R55" t="n">
-        <v>7429384</v>
+        <v>7429600</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6372,12 +6377,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6404,10 +6409,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595914</v>
+        <v>122595616</v>
       </c>
       <c r="B56" t="n">
-        <v>79843</v>
+        <v>98355</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6416,25 +6421,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800417</v>
+        <v>800708</v>
       </c>
       <c r="R56" t="n">
-        <v>7429377</v>
+        <v>7429313</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6478,12 +6483,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6510,10 +6515,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595913</v>
+        <v>122595900</v>
       </c>
       <c r="B57" t="n">
-        <v>79747</v>
+        <v>79384</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6522,25 +6527,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6554,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800413</v>
+        <v>800793</v>
       </c>
       <c r="R57" t="n">
-        <v>7429375</v>
+        <v>7429346</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6616,10 +6621,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595627</v>
+        <v>122595916</v>
       </c>
       <c r="B58" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6628,25 +6633,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800851</v>
+        <v>800420</v>
       </c>
       <c r="R58" t="n">
-        <v>7429442</v>
+        <v>7429384</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6690,12 +6695,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6722,10 +6727,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595615</v>
+        <v>122595593</v>
       </c>
       <c r="B59" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6766,10 +6771,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800705</v>
+        <v>800567</v>
       </c>
       <c r="R59" t="n">
-        <v>7429329</v>
+        <v>7429589</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6828,10 +6833,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595640</v>
+        <v>122595611</v>
       </c>
       <c r="B60" t="n">
-        <v>78499</v>
+        <v>98355</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6840,25 +6845,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6872,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800769</v>
+        <v>800599</v>
       </c>
       <c r="R60" t="n">
-        <v>7429437</v>
+        <v>7429383</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6934,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595593</v>
+        <v>122595634</v>
       </c>
       <c r="B61" t="n">
-        <v>98347</v>
+        <v>98273</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6946,25 +6951,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800567</v>
+        <v>800580</v>
       </c>
       <c r="R61" t="n">
-        <v>7429589</v>
+        <v>7429643</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7040,10 +7045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595599</v>
+        <v>122595632</v>
       </c>
       <c r="B62" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7084,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800643</v>
+        <v>800635</v>
       </c>
       <c r="R62" t="n">
-        <v>7429452</v>
+        <v>7429538</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7146,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595595</v>
+        <v>122595639</v>
       </c>
       <c r="B63" t="n">
-        <v>98347</v>
+        <v>92213</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7162,21 +7167,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>149</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800518</v>
+        <v>800773</v>
       </c>
       <c r="R63" t="n">
-        <v>7429600</v>
+        <v>7429354</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7252,10 +7257,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595592</v>
+        <v>122595911</v>
       </c>
       <c r="B64" t="n">
-        <v>98347</v>
+        <v>94380</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7264,25 +7269,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7296,10 +7301,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800614</v>
+        <v>800419</v>
       </c>
       <c r="R64" t="n">
-        <v>7429556</v>
+        <v>7429341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,12 +7331,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7358,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595634</v>
+        <v>122595913</v>
       </c>
       <c r="B65" t="n">
-        <v>98265</v>
+        <v>79751</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7374,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223591</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7402,10 +7407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800580</v>
+        <v>800413</v>
       </c>
       <c r="R65" t="n">
-        <v>7429643</v>
+        <v>7429375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,12 +7437,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7464,10 +7469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595899</v>
+        <v>122595607</v>
       </c>
       <c r="B66" t="n">
-        <v>78499</v>
+        <v>98355</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7476,25 +7481,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7508,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800751</v>
+        <v>800565</v>
       </c>
       <c r="R66" t="n">
-        <v>7429412</v>
+        <v>7429285</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7538,12 +7543,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7570,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595636</v>
+        <v>122595601</v>
       </c>
       <c r="B67" t="n">
-        <v>97307</v>
+        <v>98355</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7582,25 +7587,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7608,20 +7613,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800929</v>
+        <v>800590</v>
       </c>
       <c r="R67" t="n">
-        <v>7429308</v>
+        <v>7429490</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7662,7 +7663,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595599</v>
+        <v>122595901</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>78411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800643</v>
+        <v>800786</v>
       </c>
       <c r="R2" t="n">
-        <v>7429452</v>
+        <v>7429304</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595629</v>
+        <v>122595910</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>79751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800859</v>
+        <v>800412</v>
       </c>
       <c r="R3" t="n">
-        <v>7429527</v>
+        <v>7429327</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595602</v>
+        <v>122595618</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800439</v>
+        <v>800702</v>
       </c>
       <c r="R4" t="n">
-        <v>7429345</v>
+        <v>7429367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595606</v>
+        <v>122595900</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800535</v>
+        <v>800793</v>
       </c>
       <c r="R5" t="n">
-        <v>7429362</v>
+        <v>7429346</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595598</v>
+        <v>122595605</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800643</v>
+        <v>800481</v>
       </c>
       <c r="R6" t="n">
-        <v>7429444</v>
+        <v>7429318</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595604</v>
+        <v>122595628</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800482</v>
+        <v>800709</v>
       </c>
       <c r="R7" t="n">
-        <v>7429353</v>
+        <v>7429466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595591</v>
+        <v>122595903</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800604</v>
+        <v>800756</v>
       </c>
       <c r="R8" t="n">
-        <v>7429623</v>
+        <v>7429284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595609</v>
+        <v>122595898</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800532</v>
+        <v>800726</v>
       </c>
       <c r="R9" t="n">
-        <v>7429301</v>
+        <v>7429460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595893</v>
+        <v>122595611</v>
       </c>
       <c r="B10" t="n">
-        <v>95901</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800464</v>
+        <v>800599</v>
       </c>
       <c r="R10" t="n">
-        <v>7429456</v>
+        <v>7429383</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595906</v>
+        <v>122595623</v>
       </c>
       <c r="B11" t="n">
-        <v>79751</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800557</v>
+        <v>800714</v>
       </c>
       <c r="R11" t="n">
-        <v>7429273</v>
+        <v>7429368</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,12 +1703,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595623</v>
+        <v>122595619</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800714</v>
+        <v>800707</v>
       </c>
       <c r="R12" t="n">
-        <v>7429368</v>
+        <v>7429357</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595613</v>
+        <v>122595914</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800646</v>
+        <v>800417</v>
       </c>
       <c r="R13" t="n">
-        <v>7429350</v>
+        <v>7429377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,7 +1947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595622</v>
+        <v>122595593</v>
       </c>
       <c r="B14" t="n">
         <v>98355</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800857</v>
+        <v>800567</v>
       </c>
       <c r="R14" t="n">
-        <v>7429342</v>
+        <v>7429589</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595612</v>
+        <v>122595622</v>
       </c>
       <c r="B15" t="n">
         <v>98355</v>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800658</v>
+        <v>800857</v>
       </c>
       <c r="R15" t="n">
-        <v>7429352</v>
+        <v>7429342</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595625</v>
+        <v>122595591</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800705</v>
+        <v>800604</v>
       </c>
       <c r="R16" t="n">
-        <v>7429366</v>
+        <v>7429623</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595903</v>
+        <v>122595620</v>
       </c>
       <c r="B17" t="n">
-        <v>78503</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800756</v>
+        <v>800882</v>
       </c>
       <c r="R17" t="n">
-        <v>7429284</v>
+        <v>7429337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595910</v>
+        <v>122595633</v>
       </c>
       <c r="B18" t="n">
-        <v>79751</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800412</v>
+        <v>800657</v>
       </c>
       <c r="R18" t="n">
-        <v>7429327</v>
+        <v>7429608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595620</v>
+        <v>122595913</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>79751</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800882</v>
+        <v>800413</v>
       </c>
       <c r="R19" t="n">
-        <v>7429337</v>
+        <v>7429375</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595614</v>
+        <v>122595916</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800650</v>
+        <v>800420</v>
       </c>
       <c r="R20" t="n">
-        <v>7429351</v>
+        <v>7429384</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2689,10 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595914</v>
+        <v>122595629</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2701,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800417</v>
+        <v>800859</v>
       </c>
       <c r="R21" t="n">
-        <v>7429377</v>
+        <v>7429527</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595921</v>
+        <v>122595594</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800444</v>
+        <v>800577</v>
       </c>
       <c r="R22" t="n">
-        <v>7429388</v>
+        <v>7429596</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2901,7 +2901,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595605</v>
+        <v>122595621</v>
       </c>
       <c r="B23" t="n">
         <v>98355</v>
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800481</v>
+        <v>800914</v>
       </c>
       <c r="R23" t="n">
-        <v>7429318</v>
+        <v>7429341</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595899</v>
+        <v>122595603</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>98355</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800751</v>
+        <v>800492</v>
       </c>
       <c r="R24" t="n">
-        <v>7429412</v>
+        <v>7429368</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595902</v>
+        <v>122595598</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3125,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800768</v>
+        <v>800643</v>
       </c>
       <c r="R25" t="n">
-        <v>7429299</v>
+        <v>7429444</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3219,10 +3219,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595630</v>
+        <v>122595634</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98273</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800696</v>
+        <v>800580</v>
       </c>
       <c r="R26" t="n">
-        <v>7429504</v>
+        <v>7429643</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3325,10 +3325,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595633</v>
+        <v>122595905</v>
       </c>
       <c r="B27" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800657</v>
+        <v>800662</v>
       </c>
       <c r="R27" t="n">
-        <v>7429608</v>
+        <v>7429278</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3431,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595915</v>
+        <v>122595617</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800419</v>
+        <v>800705</v>
       </c>
       <c r="R28" t="n">
-        <v>7429379</v>
+        <v>7429310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,12 +3505,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595897</v>
+        <v>122595604</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800590</v>
+        <v>800482</v>
       </c>
       <c r="R29" t="n">
-        <v>7429518</v>
+        <v>7429353</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,7 +3643,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595596</v>
+        <v>122595614</v>
       </c>
       <c r="B30" t="n">
         <v>98355</v>
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800535</v>
+        <v>800650</v>
       </c>
       <c r="R30" t="n">
-        <v>7429581</v>
+        <v>7429351</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595628</v>
+        <v>122595595</v>
       </c>
       <c r="B31" t="n">
         <v>98355</v>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800709</v>
+        <v>800518</v>
       </c>
       <c r="R31" t="n">
-        <v>7429466</v>
+        <v>7429600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595610</v>
+        <v>122595630</v>
       </c>
       <c r="B32" t="n">
         <v>98355</v>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800519</v>
+        <v>800696</v>
       </c>
       <c r="R32" t="n">
-        <v>7429306</v>
+        <v>7429504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595624</v>
+        <v>122595893</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>95901</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,25 +3973,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800706</v>
+        <v>800464</v>
       </c>
       <c r="R33" t="n">
-        <v>7429365</v>
+        <v>7429456</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595618</v>
+        <v>122595639</v>
       </c>
       <c r="B34" t="n">
-        <v>98355</v>
+        <v>92213</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>149</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800702</v>
+        <v>800773</v>
       </c>
       <c r="R34" t="n">
-        <v>7429367</v>
+        <v>7429354</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595615</v>
+        <v>122595638</v>
       </c>
       <c r="B35" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800705</v>
+        <v>800789</v>
       </c>
       <c r="R35" t="n">
-        <v>7429329</v>
+        <v>7429366</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595638</v>
+        <v>122595592</v>
       </c>
       <c r="B36" t="n">
-        <v>92225</v>
+        <v>98355</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,25 +4291,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800789</v>
+        <v>800614</v>
       </c>
       <c r="R36" t="n">
-        <v>7429366</v>
+        <v>7429556</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595603</v>
+        <v>122595600</v>
       </c>
       <c r="B37" t="n">
         <v>98355</v>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800492</v>
+        <v>800475</v>
       </c>
       <c r="R37" t="n">
-        <v>7429368</v>
+        <v>7429573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4491,7 +4491,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595600</v>
+        <v>122595616</v>
       </c>
       <c r="B38" t="n">
         <v>98355</v>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800475</v>
+        <v>800708</v>
       </c>
       <c r="R38" t="n">
-        <v>7429573</v>
+        <v>7429313</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595592</v>
+        <v>122595607</v>
       </c>
       <c r="B39" t="n">
         <v>98355</v>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800614</v>
+        <v>800565</v>
       </c>
       <c r="R39" t="n">
-        <v>7429556</v>
+        <v>7429285</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595636</v>
+        <v>122595921</v>
       </c>
       <c r="B40" t="n">
-        <v>97315</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4715,25 +4715,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4741,20 +4741,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800929</v>
+        <v>800444</v>
       </c>
       <c r="R40" t="n">
-        <v>7429308</v>
+        <v>7429388</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4781,12 +4777,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4795,7 +4791,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4814,7 +4809,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595640</v>
+        <v>122595899</v>
       </c>
       <c r="B41" t="n">
         <v>78503</v>
@@ -4858,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800769</v>
+        <v>800751</v>
       </c>
       <c r="R41" t="n">
-        <v>7429437</v>
+        <v>7429412</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,12 +4883,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4920,10 +4915,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595905</v>
+        <v>122595902</v>
       </c>
       <c r="B42" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4936,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4964,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800662</v>
+        <v>800768</v>
       </c>
       <c r="R42" t="n">
-        <v>7429278</v>
+        <v>7429299</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5026,7 +5021,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595594</v>
+        <v>122595590</v>
       </c>
       <c r="B43" t="n">
         <v>98355</v>
@@ -5070,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800577</v>
+        <v>800672</v>
       </c>
       <c r="R43" t="n">
-        <v>7429596</v>
+        <v>7429603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5132,10 +5127,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595617</v>
+        <v>122595915</v>
       </c>
       <c r="B44" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5144,25 +5139,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5176,10 +5171,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800705</v>
+        <v>800419</v>
       </c>
       <c r="R44" t="n">
-        <v>7429310</v>
+        <v>7429379</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5206,12 +5201,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5238,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595597</v>
+        <v>122595911</v>
       </c>
       <c r="B45" t="n">
-        <v>98355</v>
+        <v>94380</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5282,10 +5277,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800611</v>
+        <v>800419</v>
       </c>
       <c r="R45" t="n">
-        <v>7429547</v>
+        <v>7429341</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5312,12 +5307,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,7 +5339,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595590</v>
+        <v>122595597</v>
       </c>
       <c r="B46" t="n">
         <v>98355</v>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800672</v>
+        <v>800611</v>
       </c>
       <c r="R46" t="n">
-        <v>7429603</v>
+        <v>7429547</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5450,7 +5445,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595627</v>
+        <v>122595625</v>
       </c>
       <c r="B47" t="n">
         <v>98355</v>
@@ -5494,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800851</v>
+        <v>800705</v>
       </c>
       <c r="R47" t="n">
-        <v>7429442</v>
+        <v>7429366</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,7 +5551,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595621</v>
+        <v>122595613</v>
       </c>
       <c r="B48" t="n">
         <v>98355</v>
@@ -5600,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800914</v>
+        <v>800646</v>
       </c>
       <c r="R48" t="n">
-        <v>7429341</v>
+        <v>7429350</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,10 +5657,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595608</v>
+        <v>122595917</v>
       </c>
       <c r="B49" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5674,25 +5669,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5706,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800522</v>
+        <v>800422</v>
       </c>
       <c r="R49" t="n">
-        <v>7429299</v>
+        <v>7429390</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5736,12 +5731,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5879,10 +5874,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595619</v>
+        <v>122595640</v>
       </c>
       <c r="B51" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5891,25 +5886,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800707</v>
+        <v>800769</v>
       </c>
       <c r="R51" t="n">
-        <v>7429357</v>
+        <v>7429437</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5985,10 +5980,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595901</v>
+        <v>122595632</v>
       </c>
       <c r="B52" t="n">
-        <v>78411</v>
+        <v>98355</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5997,25 +5992,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6029,10 +6024,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800786</v>
+        <v>800635</v>
       </c>
       <c r="R52" t="n">
-        <v>7429304</v>
+        <v>7429538</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6059,12 +6054,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6091,10 +6086,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595898</v>
+        <v>122595615</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>98355</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6103,25 +6098,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800726</v>
+        <v>800705</v>
       </c>
       <c r="R53" t="n">
-        <v>7429460</v>
+        <v>7429329</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6165,12 +6160,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595917</v>
+        <v>122595897</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,21 +6208,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6241,10 +6236,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800422</v>
+        <v>800590</v>
       </c>
       <c r="R54" t="n">
-        <v>7429390</v>
+        <v>7429518</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6303,10 +6298,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595595</v>
+        <v>122595636</v>
       </c>
       <c r="B55" t="n">
-        <v>98355</v>
+        <v>97315</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6315,25 +6310,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6341,16 +6336,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800518</v>
+        <v>800929</v>
       </c>
       <c r="R55" t="n">
-        <v>7429600</v>
+        <v>7429308</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6391,6 +6390,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6409,7 +6409,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595616</v>
+        <v>122595608</v>
       </c>
       <c r="B56" t="n">
         <v>98355</v>
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800708</v>
+        <v>800522</v>
       </c>
       <c r="R56" t="n">
-        <v>7429313</v>
+        <v>7429299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6515,10 +6515,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595900</v>
+        <v>122595596</v>
       </c>
       <c r="B57" t="n">
-        <v>79384</v>
+        <v>98355</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6527,25 +6527,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800793</v>
+        <v>800535</v>
       </c>
       <c r="R57" t="n">
-        <v>7429346</v>
+        <v>7429581</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6589,12 +6589,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6621,10 +6621,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595916</v>
+        <v>122595627</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6633,25 +6633,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6665,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800420</v>
+        <v>800851</v>
       </c>
       <c r="R58" t="n">
-        <v>7429384</v>
+        <v>7429442</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6695,12 +6695,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6727,7 +6727,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595593</v>
+        <v>122595606</v>
       </c>
       <c r="B59" t="n">
         <v>98355</v>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800567</v>
+        <v>800535</v>
       </c>
       <c r="R59" t="n">
-        <v>7429589</v>
+        <v>7429362</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595611</v>
+        <v>122595612</v>
       </c>
       <c r="B60" t="n">
         <v>98355</v>
@@ -6877,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800599</v>
+        <v>800658</v>
       </c>
       <c r="R60" t="n">
-        <v>7429383</v>
+        <v>7429352</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6939,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595634</v>
+        <v>122595906</v>
       </c>
       <c r="B61" t="n">
-        <v>98273</v>
+        <v>79751</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6955,21 +6955,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223591</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800580</v>
+        <v>800557</v>
       </c>
       <c r="R61" t="n">
-        <v>7429643</v>
+        <v>7429273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,12 +7013,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7045,7 +7045,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595632</v>
+        <v>122595624</v>
       </c>
       <c r="B62" t="n">
         <v>98355</v>
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800635</v>
+        <v>800706</v>
       </c>
       <c r="R62" t="n">
-        <v>7429538</v>
+        <v>7429365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7151,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595639</v>
+        <v>122595601</v>
       </c>
       <c r="B63" t="n">
-        <v>92213</v>
+        <v>98355</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7167,21 +7167,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800773</v>
+        <v>800590</v>
       </c>
       <c r="R63" t="n">
-        <v>7429354</v>
+        <v>7429490</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7257,10 +7257,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595911</v>
+        <v>122595599</v>
       </c>
       <c r="B64" t="n">
-        <v>94380</v>
+        <v>98355</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7269,25 +7269,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800419</v>
+        <v>800643</v>
       </c>
       <c r="R64" t="n">
-        <v>7429341</v>
+        <v>7429452</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7363,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595913</v>
+        <v>122595610</v>
       </c>
       <c r="B65" t="n">
-        <v>79751</v>
+        <v>98355</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7375,25 +7375,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7407,10 +7407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800413</v>
+        <v>800519</v>
       </c>
       <c r="R65" t="n">
-        <v>7429375</v>
+        <v>7429306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7469,7 +7469,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595607</v>
+        <v>122595609</v>
       </c>
       <c r="B66" t="n">
         <v>98355</v>
@@ -7513,10 +7513,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800565</v>
+        <v>800532</v>
       </c>
       <c r="R66" t="n">
-        <v>7429285</v>
+        <v>7429301</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7575,7 +7575,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595601</v>
+        <v>122595602</v>
       </c>
       <c r="B67" t="n">
         <v>98355</v>
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800590</v>
+        <v>800439</v>
       </c>
       <c r="R67" t="n">
-        <v>7429490</v>
+        <v>7429345</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595901</v>
+        <v>122595921</v>
       </c>
       <c r="B2" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800786</v>
+        <v>800444</v>
       </c>
       <c r="R2" t="n">
-        <v>7429304</v>
+        <v>7429388</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595910</v>
+        <v>122595609</v>
       </c>
       <c r="B3" t="n">
-        <v>79751</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800412</v>
+        <v>800532</v>
       </c>
       <c r="R3" t="n">
-        <v>7429327</v>
+        <v>7429301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,17 +880,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595618</v>
+        <v>122595612</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800702</v>
+        <v>800658</v>
       </c>
       <c r="R4" t="n">
-        <v>7429367</v>
+        <v>7429352</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595900</v>
+        <v>122595639</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>92213</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>149</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800793</v>
+        <v>800773</v>
       </c>
       <c r="R5" t="n">
-        <v>7429346</v>
+        <v>7429354</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595605</v>
+        <v>122595917</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800481</v>
+        <v>800422</v>
       </c>
       <c r="R6" t="n">
-        <v>7429318</v>
+        <v>7429390</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595628</v>
+        <v>122595911</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>94382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800709</v>
+        <v>800419</v>
       </c>
       <c r="R7" t="n">
-        <v>7429466</v>
+        <v>7429341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595903</v>
+        <v>122595622</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800756</v>
+        <v>800857</v>
       </c>
       <c r="R8" t="n">
-        <v>7429284</v>
+        <v>7429342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595898</v>
+        <v>122595632</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800726</v>
+        <v>800635</v>
       </c>
       <c r="R9" t="n">
-        <v>7429460</v>
+        <v>7429538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595611</v>
+        <v>122595628</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800599</v>
+        <v>800709</v>
       </c>
       <c r="R10" t="n">
-        <v>7429383</v>
+        <v>7429466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595623</v>
+        <v>122595638</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>92225</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1641,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800714</v>
+        <v>800789</v>
       </c>
       <c r="R11" t="n">
-        <v>7429368</v>
+        <v>7429366</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,17 +1728,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595619</v>
+        <v>122595634</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>98275</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800707</v>
+        <v>800580</v>
       </c>
       <c r="R12" t="n">
-        <v>7429357</v>
+        <v>7429643</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595914</v>
+        <v>122595893</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>95903</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800417</v>
+        <v>800464</v>
       </c>
       <c r="R13" t="n">
-        <v>7429377</v>
+        <v>7429456</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595593</v>
+        <v>122595617</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800567</v>
+        <v>800705</v>
       </c>
       <c r="R14" t="n">
-        <v>7429589</v>
+        <v>7429310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,17 +2046,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595622</v>
+        <v>122595619</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800857</v>
+        <v>800707</v>
       </c>
       <c r="R15" t="n">
-        <v>7429342</v>
+        <v>7429357</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,17 +2152,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595591</v>
+        <v>122595601</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800604</v>
+        <v>800590</v>
       </c>
       <c r="R16" t="n">
-        <v>7429623</v>
+        <v>7429490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,17 +2258,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595620</v>
+        <v>122595898</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2277,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800882</v>
+        <v>800726</v>
       </c>
       <c r="R17" t="n">
-        <v>7429337</v>
+        <v>7429460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595633</v>
+        <v>122595905</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800657</v>
+        <v>800662</v>
       </c>
       <c r="R18" t="n">
-        <v>7429608</v>
+        <v>7429278</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595916</v>
+        <v>122595593</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2595,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800420</v>
+        <v>800567</v>
       </c>
       <c r="R20" t="n">
-        <v>7429384</v>
+        <v>7429589</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2682,17 +2682,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595629</v>
+        <v>122595599</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800859</v>
+        <v>800643</v>
       </c>
       <c r="R21" t="n">
-        <v>7429527</v>
+        <v>7429452</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,17 +2788,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595594</v>
+        <v>122595910</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>79751</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800577</v>
+        <v>800412</v>
       </c>
       <c r="R22" t="n">
-        <v>7429596</v>
+        <v>7429327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2901,10 +2901,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595621</v>
+        <v>122595640</v>
       </c>
       <c r="B23" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800914</v>
+        <v>800769</v>
       </c>
       <c r="R23" t="n">
-        <v>7429341</v>
+        <v>7429437</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,17 +3000,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595603</v>
+        <v>122595900</v>
       </c>
       <c r="B24" t="n">
-        <v>98355</v>
+        <v>79384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3019,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800492</v>
+        <v>800793</v>
       </c>
       <c r="R24" t="n">
-        <v>7429368</v>
+        <v>7429346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595598</v>
+        <v>122595590</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800643</v>
+        <v>800672</v>
       </c>
       <c r="R25" t="n">
-        <v>7429444</v>
+        <v>7429603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595634</v>
+        <v>122595603</v>
       </c>
       <c r="B26" t="n">
-        <v>98273</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3231,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800580</v>
+        <v>800492</v>
       </c>
       <c r="R26" t="n">
-        <v>7429643</v>
+        <v>7429368</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,17 +3318,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595905</v>
+        <v>122595629</v>
       </c>
       <c r="B27" t="n">
-        <v>79384</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3337,25 +3337,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800662</v>
+        <v>800859</v>
       </c>
       <c r="R27" t="n">
-        <v>7429278</v>
+        <v>7429527</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3399,12 +3399,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3424,17 +3424,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595617</v>
+        <v>122595618</v>
       </c>
       <c r="B28" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800705</v>
+        <v>800702</v>
       </c>
       <c r="R28" t="n">
-        <v>7429310</v>
+        <v>7429367</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,17 +3530,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595604</v>
+        <v>122595620</v>
       </c>
       <c r="B29" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3581,10 +3581,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800482</v>
+        <v>800882</v>
       </c>
       <c r="R29" t="n">
-        <v>7429353</v>
+        <v>7429337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
         <v>122595614</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3742,17 +3742,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595595</v>
+        <v>122595621</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800518</v>
+        <v>800914</v>
       </c>
       <c r="R31" t="n">
-        <v>7429600</v>
+        <v>7429341</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,17 +3848,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595630</v>
+        <v>122595611</v>
       </c>
       <c r="B32" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800696</v>
+        <v>800599</v>
       </c>
       <c r="R32" t="n">
-        <v>7429504</v>
+        <v>7429383</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,17 +3954,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595893</v>
+        <v>122595915</v>
       </c>
       <c r="B33" t="n">
-        <v>95901</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3977,21 +3977,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800464</v>
+        <v>800419</v>
       </c>
       <c r="R33" t="n">
-        <v>7429456</v>
+        <v>7429379</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595639</v>
+        <v>122595613</v>
       </c>
       <c r="B34" t="n">
-        <v>92213</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800773</v>
+        <v>800646</v>
       </c>
       <c r="R34" t="n">
-        <v>7429354</v>
+        <v>7429350</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4166,17 +4166,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595638</v>
+        <v>122595604</v>
       </c>
       <c r="B35" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,25 +4185,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800789</v>
+        <v>800482</v>
       </c>
       <c r="R35" t="n">
-        <v>7429366</v>
+        <v>7429353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,17 +4272,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595592</v>
+        <v>122595595</v>
       </c>
       <c r="B36" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800614</v>
+        <v>800518</v>
       </c>
       <c r="R36" t="n">
-        <v>7429556</v>
+        <v>7429600</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4378,17 +4378,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595600</v>
+        <v>122595606</v>
       </c>
       <c r="B37" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800475</v>
+        <v>800535</v>
       </c>
       <c r="R37" t="n">
-        <v>7429573</v>
+        <v>7429362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4484,17 +4484,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595616</v>
+        <v>122595633</v>
       </c>
       <c r="B38" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800708</v>
+        <v>800657</v>
       </c>
       <c r="R38" t="n">
-        <v>7429313</v>
+        <v>7429608</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4590,17 +4590,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595607</v>
+        <v>122595615</v>
       </c>
       <c r="B39" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800565</v>
+        <v>800705</v>
       </c>
       <c r="R39" t="n">
-        <v>7429285</v>
+        <v>7429329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4696,17 +4696,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595921</v>
+        <v>122595914</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4719,21 +4719,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800444</v>
+        <v>800417</v>
       </c>
       <c r="R40" t="n">
-        <v>7429388</v>
+        <v>7429377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,10 +4809,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595899</v>
+        <v>122595610</v>
       </c>
       <c r="B41" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,25 +4821,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800751</v>
+        <v>800519</v>
       </c>
       <c r="R41" t="n">
-        <v>7429412</v>
+        <v>7429306</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4908,17 +4908,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595902</v>
+        <v>122595901</v>
       </c>
       <c r="B42" t="n">
-        <v>78503</v>
+        <v>78411</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800768</v>
+        <v>800786</v>
       </c>
       <c r="R42" t="n">
-        <v>7429299</v>
+        <v>7429304</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595590</v>
+        <v>122595594</v>
       </c>
       <c r="B43" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800672</v>
+        <v>800577</v>
       </c>
       <c r="R43" t="n">
-        <v>7429603</v>
+        <v>7429596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5120,17 +5120,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595915</v>
+        <v>122595602</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5139,25 +5139,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5171,10 +5171,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800419</v>
+        <v>800439</v>
       </c>
       <c r="R44" t="n">
-        <v>7429379</v>
+        <v>7429345</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5201,12 +5201,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595911</v>
+        <v>122595916</v>
       </c>
       <c r="B45" t="n">
-        <v>94380</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2387</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800419</v>
+        <v>800420</v>
       </c>
       <c r="R45" t="n">
-        <v>7429341</v>
+        <v>7429384</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595597</v>
+        <v>122595902</v>
       </c>
       <c r="B46" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,25 +5351,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800611</v>
+        <v>800768</v>
       </c>
       <c r="R46" t="n">
-        <v>7429547</v>
+        <v>7429299</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,10 +5445,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595625</v>
+        <v>122595903</v>
       </c>
       <c r="B47" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5457,25 +5457,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800705</v>
+        <v>800756</v>
       </c>
       <c r="R47" t="n">
-        <v>7429366</v>
+        <v>7429284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5551,10 +5551,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595613</v>
+        <v>122595600</v>
       </c>
       <c r="B48" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800646</v>
+        <v>800475</v>
       </c>
       <c r="R48" t="n">
-        <v>7429350</v>
+        <v>7429573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,17 +5650,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595917</v>
+        <v>122595616</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5669,25 +5669,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800422</v>
+        <v>800708</v>
       </c>
       <c r="R49" t="n">
-        <v>7429390</v>
+        <v>7429313</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5756,17 +5756,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595635</v>
+        <v>122595625</v>
       </c>
       <c r="B50" t="n">
-        <v>97315</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,25 +5775,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5801,20 +5801,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800874</v>
+        <v>800705</v>
       </c>
       <c r="R50" t="n">
-        <v>7429248</v>
+        <v>7429366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5855,7 +5851,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5867,17 +5862,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595640</v>
+        <v>122595608</v>
       </c>
       <c r="B51" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5886,25 +5881,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5918,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800769</v>
+        <v>800522</v>
       </c>
       <c r="R51" t="n">
-        <v>7429437</v>
+        <v>7429299</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5973,17 +5968,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595632</v>
+        <v>122595636</v>
       </c>
       <c r="B52" t="n">
-        <v>98355</v>
+        <v>97317</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5992,25 +5987,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6018,16 +6013,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800635</v>
+        <v>800929</v>
       </c>
       <c r="R52" t="n">
-        <v>7429538</v>
+        <v>7429308</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6068,6 +6067,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595615</v>
+        <v>122595899</v>
       </c>
       <c r="B53" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,25 +6098,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800705</v>
+        <v>800751</v>
       </c>
       <c r="R53" t="n">
-        <v>7429329</v>
+        <v>7429412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,12 +6160,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595897</v>
+        <v>122595605</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6204,25 +6204,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800590</v>
+        <v>800481</v>
       </c>
       <c r="R54" t="n">
-        <v>7429518</v>
+        <v>7429318</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6266,12 +6266,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6291,17 +6291,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595636</v>
+        <v>122595624</v>
       </c>
       <c r="B55" t="n">
-        <v>97315</v>
+        <v>98357</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,25 +6310,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -6336,20 +6336,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800929</v>
+        <v>800706</v>
       </c>
       <c r="R55" t="n">
-        <v>7429308</v>
+        <v>7429365</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6390,7 +6386,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6402,17 +6397,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595608</v>
+        <v>122595596</v>
       </c>
       <c r="B56" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6453,10 +6448,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800522</v>
+        <v>800535</v>
       </c>
       <c r="R56" t="n">
-        <v>7429299</v>
+        <v>7429581</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6508,17 +6503,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595596</v>
+        <v>122595597</v>
       </c>
       <c r="B57" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6559,10 +6554,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800535</v>
+        <v>800611</v>
       </c>
       <c r="R57" t="n">
-        <v>7429581</v>
+        <v>7429547</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,17 +6609,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595627</v>
+        <v>122595906</v>
       </c>
       <c r="B58" t="n">
-        <v>98355</v>
+        <v>79751</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6633,25 +6628,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6665,10 +6660,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800851</v>
+        <v>800557</v>
       </c>
       <c r="R58" t="n">
-        <v>7429442</v>
+        <v>7429273</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6695,12 +6690,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6727,10 +6722,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595606</v>
+        <v>122595591</v>
       </c>
       <c r="B59" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6771,10 +6766,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800535</v>
+        <v>800604</v>
       </c>
       <c r="R59" t="n">
-        <v>7429362</v>
+        <v>7429623</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6826,17 +6821,17 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595612</v>
+        <v>122595598</v>
       </c>
       <c r="B60" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6877,10 +6872,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800658</v>
+        <v>800643</v>
       </c>
       <c r="R60" t="n">
-        <v>7429352</v>
+        <v>7429444</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6932,17 +6927,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595906</v>
+        <v>122595630</v>
       </c>
       <c r="B61" t="n">
-        <v>79751</v>
+        <v>98357</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6951,25 +6946,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6983,10 +6978,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800557</v>
+        <v>800696</v>
       </c>
       <c r="R61" t="n">
-        <v>7429273</v>
+        <v>7429504</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,12 +7008,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7038,17 +7033,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595624</v>
+        <v>122595623</v>
       </c>
       <c r="B62" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7089,10 +7084,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800706</v>
+        <v>800714</v>
       </c>
       <c r="R62" t="n">
-        <v>7429365</v>
+        <v>7429368</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7144,17 +7139,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595601</v>
+        <v>122595627</v>
       </c>
       <c r="B63" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7195,10 +7190,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800590</v>
+        <v>800851</v>
       </c>
       <c r="R63" t="n">
-        <v>7429490</v>
+        <v>7429442</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7250,17 +7245,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595599</v>
+        <v>122595607</v>
       </c>
       <c r="B64" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7301,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800643</v>
+        <v>800565</v>
       </c>
       <c r="R64" t="n">
-        <v>7429452</v>
+        <v>7429285</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7356,17 +7351,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595610</v>
+        <v>122595592</v>
       </c>
       <c r="B65" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7407,10 +7402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800519</v>
+        <v>800614</v>
       </c>
       <c r="R65" t="n">
-        <v>7429306</v>
+        <v>7429556</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7462,17 +7457,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595609</v>
+        <v>122595897</v>
       </c>
       <c r="B66" t="n">
-        <v>98355</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7481,25 +7476,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7513,10 +7508,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800532</v>
+        <v>800590</v>
       </c>
       <c r="R66" t="n">
-        <v>7429301</v>
+        <v>7429518</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7543,12 +7538,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7575,10 +7570,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595602</v>
+        <v>122595635</v>
       </c>
       <c r="B67" t="n">
-        <v>98355</v>
+        <v>97317</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7587,25 +7582,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7613,16 +7608,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800439</v>
+        <v>800874</v>
       </c>
       <c r="R67" t="n">
-        <v>7429345</v>
+        <v>7429248</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7663,6 +7662,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595639</v>
+        <v>122595917</v>
       </c>
       <c r="B5" t="n">
-        <v>92213</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>149</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800773</v>
+        <v>800422</v>
       </c>
       <c r="R5" t="n">
-        <v>7429354</v>
+        <v>7429390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595917</v>
+        <v>122595639</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>92213</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>149</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800422</v>
+        <v>800773</v>
       </c>
       <c r="R6" t="n">
-        <v>7429390</v>
+        <v>7429354</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,17 +1198,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595911</v>
+        <v>122595622</v>
       </c>
       <c r="B7" t="n">
-        <v>94382</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800419</v>
+        <v>800857</v>
       </c>
       <c r="R7" t="n">
-        <v>7429341</v>
+        <v>7429342</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595622</v>
+        <v>122595632</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800857</v>
+        <v>800635</v>
       </c>
       <c r="R8" t="n">
-        <v>7429342</v>
+        <v>7429538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595632</v>
+        <v>122595628</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800635</v>
+        <v>800709</v>
       </c>
       <c r="R9" t="n">
-        <v>7429538</v>
+        <v>7429466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595628</v>
+        <v>122595911</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>94382</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800709</v>
+        <v>800419</v>
       </c>
       <c r="R10" t="n">
-        <v>7429466</v>
+        <v>7429341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595634</v>
+        <v>122595893</v>
       </c>
       <c r="B12" t="n">
-        <v>98275</v>
+        <v>95903</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223591</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800580</v>
+        <v>800464</v>
       </c>
       <c r="R12" t="n">
-        <v>7429643</v>
+        <v>7429456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,12 +1809,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595893</v>
+        <v>122595634</v>
       </c>
       <c r="B13" t="n">
-        <v>95903</v>
+        <v>98275</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800464</v>
+        <v>800580</v>
       </c>
       <c r="R13" t="n">
-        <v>7429456</v>
+        <v>7429643</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595915</v>
+        <v>122595613</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,25 +3973,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800419</v>
+        <v>800646</v>
       </c>
       <c r="R33" t="n">
-        <v>7429379</v>
+        <v>7429350</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,17 +4060,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595613</v>
+        <v>122595915</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4079,25 +4079,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800646</v>
+        <v>800419</v>
       </c>
       <c r="R34" t="n">
-        <v>7429350</v>
+        <v>7429379</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595902</v>
+        <v>122595600</v>
       </c>
       <c r="B46" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,25 +5351,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800768</v>
+        <v>800475</v>
       </c>
       <c r="R46" t="n">
-        <v>7429299</v>
+        <v>7429573</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595903</v>
+        <v>122595616</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5457,25 +5457,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800756</v>
+        <v>800708</v>
       </c>
       <c r="R47" t="n">
-        <v>7429284</v>
+        <v>7429313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5544,14 +5544,14 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595600</v>
+        <v>122595625</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800475</v>
+        <v>800705</v>
       </c>
       <c r="R48" t="n">
-        <v>7429573</v>
+        <v>7429366</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595616</v>
+        <v>122595608</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800708</v>
+        <v>800522</v>
       </c>
       <c r="R49" t="n">
-        <v>7429313</v>
+        <v>7429299</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595625</v>
+        <v>122595902</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,25 +5775,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800705</v>
+        <v>800768</v>
       </c>
       <c r="R50" t="n">
-        <v>7429366</v>
+        <v>7429299</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,12 +5837,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5862,17 +5862,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595608</v>
+        <v>122595903</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800522</v>
+        <v>800756</v>
       </c>
       <c r="R51" t="n">
-        <v>7429299</v>
+        <v>7429284</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595622</v>
+        <v>122595911</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>94382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800857</v>
+        <v>800419</v>
       </c>
       <c r="R7" t="n">
-        <v>7429342</v>
+        <v>7429341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595632</v>
+        <v>122595622</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800635</v>
+        <v>800857</v>
       </c>
       <c r="R8" t="n">
-        <v>7429538</v>
+        <v>7429342</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595628</v>
+        <v>122595632</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800709</v>
+        <v>800635</v>
       </c>
       <c r="R9" t="n">
-        <v>7429466</v>
+        <v>7429538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595911</v>
+        <v>122595628</v>
       </c>
       <c r="B10" t="n">
-        <v>94382</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800419</v>
+        <v>800709</v>
       </c>
       <c r="R10" t="n">
-        <v>7429341</v>
+        <v>7429466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -2795,10 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595910</v>
+        <v>122595640</v>
       </c>
       <c r="B22" t="n">
-        <v>79751</v>
+        <v>78503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2807,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800412</v>
+        <v>800769</v>
       </c>
       <c r="R22" t="n">
-        <v>7429327</v>
+        <v>7429437</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,12 +2869,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595640</v>
+        <v>122595910</v>
       </c>
       <c r="B23" t="n">
-        <v>78503</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800769</v>
+        <v>800412</v>
       </c>
       <c r="R23" t="n">
-        <v>7429437</v>
+        <v>7429327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595600</v>
+        <v>122595902</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,25 +5351,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800475</v>
+        <v>800768</v>
       </c>
       <c r="R46" t="n">
-        <v>7429573</v>
+        <v>7429299</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595616</v>
+        <v>122595903</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5457,25 +5457,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800708</v>
+        <v>800756</v>
       </c>
       <c r="R47" t="n">
-        <v>7429313</v>
+        <v>7429284</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5544,14 +5544,14 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595625</v>
+        <v>122595600</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800705</v>
+        <v>800475</v>
       </c>
       <c r="R48" t="n">
-        <v>7429366</v>
+        <v>7429573</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595608</v>
+        <v>122595616</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800522</v>
+        <v>800708</v>
       </c>
       <c r="R49" t="n">
-        <v>7429299</v>
+        <v>7429313</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5763,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595902</v>
+        <v>122595625</v>
       </c>
       <c r="B50" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5775,25 +5775,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5807,10 +5807,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800768</v>
+        <v>800705</v>
       </c>
       <c r="R50" t="n">
-        <v>7429299</v>
+        <v>7429366</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5837,12 +5837,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5862,17 +5862,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595903</v>
+        <v>122595608</v>
       </c>
       <c r="B51" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5881,25 +5881,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800756</v>
+        <v>800522</v>
       </c>
       <c r="R51" t="n">
-        <v>7429284</v>
+        <v>7429299</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595921</v>
+        <v>122595635</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>97317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800444</v>
+        <v>800874</v>
       </c>
       <c r="R2" t="n">
-        <v>7429388</v>
+        <v>7429248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595609</v>
+        <v>122595602</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800532</v>
+        <v>800439</v>
       </c>
       <c r="R3" t="n">
-        <v>7429301</v>
+        <v>7429345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,14 +885,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595612</v>
+        <v>122595625</v>
       </c>
       <c r="B4" t="n">
         <v>98357</v>
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800658</v>
+        <v>800705</v>
       </c>
       <c r="R4" t="n">
-        <v>7429352</v>
+        <v>7429366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,17 +991,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595917</v>
+        <v>122595893</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>95903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800422</v>
+        <v>800464</v>
       </c>
       <c r="R5" t="n">
-        <v>7429390</v>
+        <v>7429456</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595639</v>
+        <v>122595901</v>
       </c>
       <c r="B6" t="n">
-        <v>92213</v>
+        <v>78411</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>149</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800773</v>
+        <v>800786</v>
       </c>
       <c r="R6" t="n">
-        <v>7429354</v>
+        <v>7429304</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1178,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,17 +1203,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595911</v>
+        <v>122595617</v>
       </c>
       <c r="B7" t="n">
-        <v>94382</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800419</v>
+        <v>800705</v>
       </c>
       <c r="R7" t="n">
-        <v>7429341</v>
+        <v>7429310</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,12 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595622</v>
+        <v>122595592</v>
       </c>
       <c r="B8" t="n">
         <v>98357</v>
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800857</v>
+        <v>800614</v>
       </c>
       <c r="R8" t="n">
-        <v>7429342</v>
+        <v>7429556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,14 +1415,14 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595632</v>
+        <v>122595608</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1461,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800635</v>
+        <v>800522</v>
       </c>
       <c r="R9" t="n">
-        <v>7429538</v>
+        <v>7429299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,17 +1521,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595628</v>
+        <v>122595900</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1567,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800709</v>
+        <v>800793</v>
       </c>
       <c r="R10" t="n">
-        <v>7429466</v>
+        <v>7429346</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,12 +1602,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,17 +1627,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595638</v>
+        <v>122595600</v>
       </c>
       <c r="B11" t="n">
-        <v>92225</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800789</v>
+        <v>800475</v>
       </c>
       <c r="R11" t="n">
-        <v>7429366</v>
+        <v>7429573</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1728,17 +1733,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595893</v>
+        <v>122595915</v>
       </c>
       <c r="B12" t="n">
-        <v>95903</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800464</v>
+        <v>800419</v>
       </c>
       <c r="R12" t="n">
-        <v>7429456</v>
+        <v>7429379</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595634</v>
+        <v>122595616</v>
       </c>
       <c r="B13" t="n">
-        <v>98275</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1885,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800580</v>
+        <v>800708</v>
       </c>
       <c r="R13" t="n">
-        <v>7429643</v>
+        <v>7429313</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1940,17 +1945,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595617</v>
+        <v>122595910</v>
       </c>
       <c r="B14" t="n">
-        <v>98357</v>
+        <v>79751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1991,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800705</v>
+        <v>800412</v>
       </c>
       <c r="R14" t="n">
-        <v>7429310</v>
+        <v>7429327</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,12 +2026,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2051,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2152,14 +2157,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595601</v>
+        <v>122595620</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800590</v>
+        <v>800882</v>
       </c>
       <c r="R16" t="n">
-        <v>7429490</v>
+        <v>7429337</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,17 +2263,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595898</v>
+        <v>122595607</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,25 +2282,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2309,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800726</v>
+        <v>800565</v>
       </c>
       <c r="R17" t="n">
-        <v>7429460</v>
+        <v>7429285</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2339,12 +2344,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595905</v>
+        <v>122595640</v>
       </c>
       <c r="B18" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2415,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800662</v>
+        <v>800769</v>
       </c>
       <c r="R18" t="n">
-        <v>7429278</v>
+        <v>7429437</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,12 +2450,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2477,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595913</v>
+        <v>122595899</v>
       </c>
       <c r="B19" t="n">
-        <v>79751</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2489,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800413</v>
+        <v>800751</v>
       </c>
       <c r="R19" t="n">
-        <v>7429375</v>
+        <v>7429412</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595593</v>
+        <v>122595902</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2627,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800567</v>
+        <v>800768</v>
       </c>
       <c r="R20" t="n">
-        <v>7429589</v>
+        <v>7429299</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2657,12 +2662,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2682,17 +2687,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595599</v>
+        <v>122595898</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2701,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2733,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800643</v>
+        <v>800726</v>
       </c>
       <c r="R21" t="n">
-        <v>7429452</v>
+        <v>7429460</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,12 +2768,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2788,17 +2793,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595640</v>
+        <v>122595628</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2807,25 +2812,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2839,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800769</v>
+        <v>800709</v>
       </c>
       <c r="R22" t="n">
-        <v>7429437</v>
+        <v>7429466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,17 +2899,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595910</v>
+        <v>122595633</v>
       </c>
       <c r="B23" t="n">
-        <v>79751</v>
+        <v>98357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2945,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800412</v>
+        <v>800657</v>
       </c>
       <c r="R23" t="n">
-        <v>7429327</v>
+        <v>7429608</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,12 +2980,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3007,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595900</v>
+        <v>122595599</v>
       </c>
       <c r="B24" t="n">
-        <v>79384</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3051,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800793</v>
+        <v>800643</v>
       </c>
       <c r="R24" t="n">
-        <v>7429346</v>
+        <v>7429452</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,12 +3086,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595590</v>
+        <v>122595634</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98275</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3157,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800672</v>
+        <v>800580</v>
       </c>
       <c r="R25" t="n">
-        <v>7429603</v>
+        <v>7429643</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3212,17 +3217,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595603</v>
+        <v>122595897</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800492</v>
+        <v>800590</v>
       </c>
       <c r="R26" t="n">
-        <v>7429368</v>
+        <v>7429518</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3293,12 +3298,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,17 +3323,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595629</v>
+        <v>122595639</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>92213</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3341,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>149</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3369,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800859</v>
+        <v>800773</v>
       </c>
       <c r="R27" t="n">
-        <v>7429527</v>
+        <v>7429354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,17 +3429,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595618</v>
+        <v>122595638</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3443,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800702</v>
+        <v>800789</v>
       </c>
       <c r="R28" t="n">
-        <v>7429367</v>
+        <v>7429366</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3530,17 +3535,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595620</v>
+        <v>122595917</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,25 +3554,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3581,10 +3586,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800882</v>
+        <v>800422</v>
       </c>
       <c r="R29" t="n">
-        <v>7429337</v>
+        <v>7429390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3611,12 +3616,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3636,14 +3641,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595614</v>
+        <v>122595597</v>
       </c>
       <c r="B30" t="n">
         <v>98357</v>
@@ -3687,10 +3692,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800650</v>
+        <v>800611</v>
       </c>
       <c r="R30" t="n">
-        <v>7429351</v>
+        <v>7429547</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3742,14 +3747,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595621</v>
+        <v>122595594</v>
       </c>
       <c r="B31" t="n">
         <v>98357</v>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800914</v>
+        <v>800577</v>
       </c>
       <c r="R31" t="n">
-        <v>7429341</v>
+        <v>7429596</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,14 +3853,14 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595611</v>
+        <v>122595630</v>
       </c>
       <c r="B32" t="n">
         <v>98357</v>
@@ -3899,10 +3904,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800599</v>
+        <v>800696</v>
       </c>
       <c r="R32" t="n">
-        <v>7429383</v>
+        <v>7429504</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3954,17 +3959,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595613</v>
+        <v>122595903</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3973,25 +3978,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4005,10 +4010,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800646</v>
+        <v>800756</v>
       </c>
       <c r="R33" t="n">
-        <v>7429350</v>
+        <v>7429284</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,12 +4040,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4060,17 +4065,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595915</v>
+        <v>122595603</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4079,25 +4084,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4111,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800419</v>
+        <v>800492</v>
       </c>
       <c r="R34" t="n">
-        <v>7429379</v>
+        <v>7429368</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4141,12 +4146,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4173,7 +4178,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595604</v>
+        <v>122595613</v>
       </c>
       <c r="B35" t="n">
         <v>98357</v>
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800482</v>
+        <v>800646</v>
       </c>
       <c r="R35" t="n">
-        <v>7429353</v>
+        <v>7429350</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,7 +4277,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4378,17 +4383,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595606</v>
+        <v>122595905</v>
       </c>
       <c r="B37" t="n">
-        <v>98357</v>
+        <v>79384</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4397,25 +4402,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4429,10 +4434,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800535</v>
+        <v>800662</v>
       </c>
       <c r="R37" t="n">
-        <v>7429362</v>
+        <v>7429278</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,12 +4464,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4484,17 +4489,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595633</v>
+        <v>122595921</v>
       </c>
       <c r="B38" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4503,25 +4508,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4535,10 +4540,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800657</v>
+        <v>800444</v>
       </c>
       <c r="R38" t="n">
-        <v>7429608</v>
+        <v>7429388</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,12 +4570,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4590,17 +4595,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595615</v>
+        <v>122595914</v>
       </c>
       <c r="B39" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4609,25 +4614,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4641,10 +4646,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800705</v>
+        <v>800417</v>
       </c>
       <c r="R39" t="n">
-        <v>7429329</v>
+        <v>7429377</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,12 +4676,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4696,17 +4701,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595914</v>
+        <v>122595906</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4715,25 +4720,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4747,10 +4752,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800417</v>
+        <v>800557</v>
       </c>
       <c r="R40" t="n">
-        <v>7429377</v>
+        <v>7429273</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4809,7 +4814,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595610</v>
+        <v>122595598</v>
       </c>
       <c r="B41" t="n">
         <v>98357</v>
@@ -4853,10 +4858,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800519</v>
+        <v>800643</v>
       </c>
       <c r="R41" t="n">
-        <v>7429306</v>
+        <v>7429444</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,17 +4913,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595901</v>
+        <v>122595623</v>
       </c>
       <c r="B42" t="n">
-        <v>78411</v>
+        <v>98357</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4927,25 +4932,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4959,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800786</v>
+        <v>800714</v>
       </c>
       <c r="R42" t="n">
-        <v>7429304</v>
+        <v>7429368</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,12 +4994,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5021,7 +5026,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595594</v>
+        <v>122595627</v>
       </c>
       <c r="B43" t="n">
         <v>98357</v>
@@ -5065,10 +5070,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800577</v>
+        <v>800851</v>
       </c>
       <c r="R43" t="n">
-        <v>7429596</v>
+        <v>7429442</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5120,14 +5125,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595602</v>
+        <v>122595596</v>
       </c>
       <c r="B44" t="n">
         <v>98357</v>
@@ -5171,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800439</v>
+        <v>800535</v>
       </c>
       <c r="R44" t="n">
-        <v>7429345</v>
+        <v>7429581</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5226,17 +5231,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595916</v>
+        <v>122595615</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>98357</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,25 +5250,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5277,10 +5282,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800420</v>
+        <v>800705</v>
       </c>
       <c r="R45" t="n">
-        <v>7429384</v>
+        <v>7429329</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5307,12 +5312,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5339,10 +5344,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595902</v>
+        <v>122595604</v>
       </c>
       <c r="B46" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5351,25 +5356,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800768</v>
+        <v>800482</v>
       </c>
       <c r="R46" t="n">
-        <v>7429299</v>
+        <v>7429353</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,12 +5418,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5445,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595903</v>
+        <v>122595618</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5457,25 +5462,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5489,10 +5494,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800756</v>
+        <v>800702</v>
       </c>
       <c r="R47" t="n">
-        <v>7429284</v>
+        <v>7429367</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5519,12 +5524,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5551,7 +5556,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595600</v>
+        <v>122595601</v>
       </c>
       <c r="B48" t="n">
         <v>98357</v>
@@ -5595,10 +5600,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800475</v>
+        <v>800590</v>
       </c>
       <c r="R48" t="n">
-        <v>7429573</v>
+        <v>7429490</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,14 +5655,14 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595616</v>
+        <v>122595590</v>
       </c>
       <c r="B49" t="n">
         <v>98357</v>
@@ -5701,10 +5706,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800708</v>
+        <v>800672</v>
       </c>
       <c r="R49" t="n">
-        <v>7429313</v>
+        <v>7429603</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,14 +5761,14 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595625</v>
+        <v>122595612</v>
       </c>
       <c r="B50" t="n">
         <v>98357</v>
@@ -5807,10 +5812,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800705</v>
+        <v>800658</v>
       </c>
       <c r="R50" t="n">
-        <v>7429366</v>
+        <v>7429352</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5862,14 +5867,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595608</v>
+        <v>122595621</v>
       </c>
       <c r="B51" t="n">
         <v>98357</v>
@@ -5913,10 +5918,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800522</v>
+        <v>800914</v>
       </c>
       <c r="R51" t="n">
-        <v>7429299</v>
+        <v>7429341</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5968,17 +5973,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595636</v>
+        <v>122595629</v>
       </c>
       <c r="B52" t="n">
-        <v>97317</v>
+        <v>98357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5987,25 +5992,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6013,20 +6018,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800929</v>
+        <v>800859</v>
       </c>
       <c r="R52" t="n">
-        <v>7429308</v>
+        <v>7429527</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,7 +6068,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6079,17 +6079,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595899</v>
+        <v>122595624</v>
       </c>
       <c r="B53" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6098,25 +6098,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800751</v>
+        <v>800706</v>
       </c>
       <c r="R53" t="n">
-        <v>7429412</v>
+        <v>7429365</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,12 +6160,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6192,7 +6192,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595605</v>
+        <v>122595614</v>
       </c>
       <c r="B54" t="n">
         <v>98357</v>
@@ -6236,10 +6236,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800481</v>
+        <v>800650</v>
       </c>
       <c r="R54" t="n">
-        <v>7429318</v>
+        <v>7429351</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6291,14 +6291,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595624</v>
+        <v>122595609</v>
       </c>
       <c r="B55" t="n">
         <v>98357</v>
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800706</v>
+        <v>800532</v>
       </c>
       <c r="R55" t="n">
-        <v>7429365</v>
+        <v>7429301</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6397,14 +6397,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595596</v>
+        <v>122595606</v>
       </c>
       <c r="B56" t="n">
         <v>98357</v>
@@ -6451,7 +6451,7 @@
         <v>800535</v>
       </c>
       <c r="R56" t="n">
-        <v>7429581</v>
+        <v>7429362</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6503,14 +6503,14 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595597</v>
+        <v>122595605</v>
       </c>
       <c r="B57" t="n">
         <v>98357</v>
@@ -6554,10 +6554,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800611</v>
+        <v>800481</v>
       </c>
       <c r="R57" t="n">
-        <v>7429547</v>
+        <v>7429318</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6609,17 +6609,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595906</v>
+        <v>122595622</v>
       </c>
       <c r="B58" t="n">
-        <v>79751</v>
+        <v>98357</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6628,25 +6628,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6660,10 +6660,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800557</v>
+        <v>800857</v>
       </c>
       <c r="R58" t="n">
-        <v>7429273</v>
+        <v>7429342</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595598</v>
+        <v>122595593</v>
       </c>
       <c r="B60" t="n">
         <v>98357</v>
@@ -6872,10 +6872,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800643</v>
+        <v>800567</v>
       </c>
       <c r="R60" t="n">
-        <v>7429444</v>
+        <v>7429589</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595630</v>
+        <v>122595610</v>
       </c>
       <c r="B61" t="n">
         <v>98357</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800696</v>
+        <v>800519</v>
       </c>
       <c r="R61" t="n">
-        <v>7429504</v>
+        <v>7429306</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7033,14 +7033,14 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595623</v>
+        <v>122595632</v>
       </c>
       <c r="B62" t="n">
         <v>98357</v>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800714</v>
+        <v>800635</v>
       </c>
       <c r="R62" t="n">
-        <v>7429368</v>
+        <v>7429538</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7139,14 +7139,14 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595627</v>
+        <v>122595611</v>
       </c>
       <c r="B63" t="n">
         <v>98357</v>
@@ -7190,10 +7190,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800851</v>
+        <v>800599</v>
       </c>
       <c r="R63" t="n">
-        <v>7429442</v>
+        <v>7429383</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7245,17 +7245,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595607</v>
+        <v>122595916</v>
       </c>
       <c r="B64" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7264,25 +7264,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7296,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800565</v>
+        <v>800420</v>
       </c>
       <c r="R64" t="n">
-        <v>7429285</v>
+        <v>7429384</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,12 +7326,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595592</v>
+        <v>122595913</v>
       </c>
       <c r="B65" t="n">
-        <v>98357</v>
+        <v>79751</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7370,25 +7370,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800614</v>
+        <v>800413</v>
       </c>
       <c r="R65" t="n">
-        <v>7429556</v>
+        <v>7429375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7457,17 +7457,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595897</v>
+        <v>122595636</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>97317</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7476,25 +7476,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7502,16 +7502,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800590</v>
+        <v>800929</v>
       </c>
       <c r="R66" t="n">
-        <v>7429518</v>
+        <v>7429308</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7538,12 +7542,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7552,6 +7556,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7570,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595635</v>
+        <v>122595911</v>
       </c>
       <c r="B67" t="n">
-        <v>97317</v>
+        <v>94382</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7586,21 +7591,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>2387</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7608,20 +7613,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800874</v>
+        <v>800419</v>
       </c>
       <c r="R67" t="n">
-        <v>7429248</v>
+        <v>7429341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7648,12 +7649,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7662,7 +7663,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595633</v>
+        <v>122595897</v>
       </c>
       <c r="B23" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800657</v>
+        <v>800590</v>
       </c>
       <c r="R23" t="n">
-        <v>7429608</v>
+        <v>7429518</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,7 +3012,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595599</v>
+        <v>122595633</v>
       </c>
       <c r="B24" t="n">
         <v>98357</v>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800643</v>
+        <v>800657</v>
       </c>
       <c r="R24" t="n">
-        <v>7429452</v>
+        <v>7429608</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595634</v>
+        <v>122595599</v>
       </c>
       <c r="B25" t="n">
-        <v>98275</v>
+        <v>98357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800580</v>
+        <v>800643</v>
       </c>
       <c r="R25" t="n">
-        <v>7429643</v>
+        <v>7429452</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595897</v>
+        <v>122595634</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>98275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>223591</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800590</v>
+        <v>800580</v>
       </c>
       <c r="R26" t="n">
-        <v>7429518</v>
+        <v>7429643</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595639</v>
+        <v>122595597</v>
       </c>
       <c r="B27" t="n">
-        <v>92213</v>
+        <v>98357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800773</v>
+        <v>800611</v>
       </c>
       <c r="R27" t="n">
-        <v>7429354</v>
+        <v>7429547</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595638</v>
+        <v>122595639</v>
       </c>
       <c r="B28" t="n">
-        <v>92225</v>
+        <v>92213</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>149</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800789</v>
+        <v>800773</v>
       </c>
       <c r="R28" t="n">
-        <v>7429366</v>
+        <v>7429354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595597</v>
+        <v>122595638</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>92225</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,25 +3660,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800611</v>
+        <v>800789</v>
       </c>
       <c r="R30" t="n">
-        <v>7429547</v>
+        <v>7429366</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595620</v>
+        <v>122595898</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800882</v>
+        <v>800726</v>
       </c>
       <c r="R16" t="n">
-        <v>7429337</v>
+        <v>7429460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595607</v>
+        <v>122595620</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800565</v>
+        <v>800882</v>
       </c>
       <c r="R17" t="n">
-        <v>7429285</v>
+        <v>7429337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595640</v>
+        <v>122595607</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800769</v>
+        <v>800565</v>
       </c>
       <c r="R18" t="n">
-        <v>7429437</v>
+        <v>7429285</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595899</v>
+        <v>122595640</v>
       </c>
       <c r="B19" t="n">
         <v>78503</v>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800751</v>
+        <v>800769</v>
       </c>
       <c r="R19" t="n">
-        <v>7429412</v>
+        <v>7429437</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595902</v>
+        <v>122595899</v>
       </c>
       <c r="B20" t="n">
         <v>78503</v>
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800768</v>
+        <v>800751</v>
       </c>
       <c r="R20" t="n">
-        <v>7429299</v>
+        <v>7429412</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595898</v>
+        <v>122595902</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2710,21 +2710,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800726</v>
+        <v>800768</v>
       </c>
       <c r="R21" t="n">
-        <v>7429460</v>
+        <v>7429299</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595635</v>
+        <v>122595917</v>
       </c>
       <c r="B2" t="n">
-        <v>97317</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,20 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800874</v>
+        <v>800422</v>
       </c>
       <c r="R2" t="n">
-        <v>7429248</v>
+        <v>7429390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595602</v>
+        <v>122595604</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800439</v>
+        <v>800482</v>
       </c>
       <c r="R3" t="n">
-        <v>7429345</v>
+        <v>7429353</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595625</v>
+        <v>122595618</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800705</v>
+        <v>800702</v>
       </c>
       <c r="R4" t="n">
-        <v>7429366</v>
+        <v>7429367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595893</v>
+        <v>122595638</v>
       </c>
       <c r="B5" t="n">
-        <v>95903</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800464</v>
+        <v>800789</v>
       </c>
       <c r="R5" t="n">
-        <v>7429456</v>
+        <v>7429366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595901</v>
+        <v>122595593</v>
       </c>
       <c r="B6" t="n">
-        <v>78411</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1148,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800786</v>
+        <v>800567</v>
       </c>
       <c r="R6" t="n">
-        <v>7429304</v>
+        <v>7429589</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,12 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595617</v>
+        <v>122595640</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800705</v>
+        <v>800769</v>
       </c>
       <c r="R7" t="n">
-        <v>7429310</v>
+        <v>7429437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595592</v>
+        <v>122595610</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800614</v>
+        <v>800519</v>
       </c>
       <c r="R8" t="n">
-        <v>7429556</v>
+        <v>7429306</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595608</v>
+        <v>122595635</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>97325</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1460,16 +1455,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800522</v>
+        <v>800874</v>
       </c>
       <c r="R9" t="n">
-        <v>7429299</v>
+        <v>7429248</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,6 +1509,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1528,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595900</v>
+        <v>122595893</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>95911</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800793</v>
+        <v>800464</v>
       </c>
       <c r="R10" t="n">
-        <v>7429346</v>
+        <v>7429456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595600</v>
+        <v>122595897</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800475</v>
+        <v>800590</v>
       </c>
       <c r="R11" t="n">
-        <v>7429573</v>
+        <v>7429518</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595915</v>
+        <v>122595913</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800419</v>
+        <v>800413</v>
       </c>
       <c r="R12" t="n">
-        <v>7429379</v>
+        <v>7429375</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595616</v>
+        <v>122595623</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800708</v>
+        <v>800714</v>
       </c>
       <c r="R13" t="n">
-        <v>7429313</v>
+        <v>7429368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595910</v>
+        <v>122595599</v>
       </c>
       <c r="B14" t="n">
-        <v>79751</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800412</v>
+        <v>800643</v>
       </c>
       <c r="R14" t="n">
-        <v>7429327</v>
+        <v>7429452</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,7 +2061,7 @@
         <v>122595619</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595898</v>
+        <v>122595615</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2176,25 +2176,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800726</v>
+        <v>800705</v>
       </c>
       <c r="R16" t="n">
-        <v>7429460</v>
+        <v>7429329</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,12 +2238,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595620</v>
+        <v>122595632</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800882</v>
+        <v>800635</v>
       </c>
       <c r="R17" t="n">
-        <v>7429337</v>
+        <v>7429538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595607</v>
+        <v>122595903</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,25 +2388,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800565</v>
+        <v>800756</v>
       </c>
       <c r="R18" t="n">
-        <v>7429285</v>
+        <v>7429284</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2482,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595640</v>
+        <v>122595627</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800769</v>
+        <v>800851</v>
       </c>
       <c r="R19" t="n">
-        <v>7429437</v>
+        <v>7429442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595899</v>
+        <v>122595628</v>
       </c>
       <c r="B20" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,25 +2600,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2632,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800751</v>
+        <v>800709</v>
       </c>
       <c r="R20" t="n">
-        <v>7429412</v>
+        <v>7429466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595902</v>
+        <v>122595625</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800768</v>
+        <v>800705</v>
       </c>
       <c r="R21" t="n">
-        <v>7429299</v>
+        <v>7429366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595628</v>
+        <v>122595616</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800709</v>
+        <v>800708</v>
       </c>
       <c r="R22" t="n">
-        <v>7429466</v>
+        <v>7429313</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595897</v>
+        <v>122595611</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2918,25 +2918,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800590</v>
+        <v>800599</v>
       </c>
       <c r="R23" t="n">
-        <v>7429518</v>
+        <v>7429383</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,12 +2980,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595633</v>
+        <v>122595916</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3024,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800657</v>
+        <v>800420</v>
       </c>
       <c r="R24" t="n">
-        <v>7429608</v>
+        <v>7429384</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,10 +3118,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595599</v>
+        <v>122595634</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>98283</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,25 +3130,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>223591</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800643</v>
+        <v>800580</v>
       </c>
       <c r="R25" t="n">
-        <v>7429452</v>
+        <v>7429643</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595634</v>
+        <v>122595630</v>
       </c>
       <c r="B26" t="n">
-        <v>98275</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3236,25 +3236,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>223591</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800580</v>
+        <v>800696</v>
       </c>
       <c r="R26" t="n">
-        <v>7429643</v>
+        <v>7429504</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595597</v>
+        <v>122595590</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800611</v>
+        <v>800672</v>
       </c>
       <c r="R27" t="n">
-        <v>7429547</v>
+        <v>7429603</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3436,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595639</v>
+        <v>122595608</v>
       </c>
       <c r="B28" t="n">
-        <v>92213</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,21 +3452,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3480,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800773</v>
+        <v>800522</v>
       </c>
       <c r="R28" t="n">
-        <v>7429354</v>
+        <v>7429299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595917</v>
+        <v>122595601</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3554,25 +3554,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800422</v>
+        <v>800590</v>
       </c>
       <c r="R29" t="n">
-        <v>7429390</v>
+        <v>7429490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3648,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595638</v>
+        <v>122595600</v>
       </c>
       <c r="B30" t="n">
-        <v>92225</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,25 +3660,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800789</v>
+        <v>800475</v>
       </c>
       <c r="R30" t="n">
-        <v>7429366</v>
+        <v>7429573</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595594</v>
+        <v>122595633</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800577</v>
+        <v>800657</v>
       </c>
       <c r="R31" t="n">
-        <v>7429596</v>
+        <v>7429608</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595630</v>
+        <v>122595613</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800696</v>
+        <v>800646</v>
       </c>
       <c r="R32" t="n">
-        <v>7429504</v>
+        <v>7429350</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595903</v>
+        <v>122595902</v>
       </c>
       <c r="B33" t="n">
         <v>78503</v>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800756</v>
+        <v>800768</v>
       </c>
       <c r="R33" t="n">
-        <v>7429284</v>
+        <v>7429299</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4072,10 +4072,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595603</v>
+        <v>122595606</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800492</v>
+        <v>800535</v>
       </c>
       <c r="R34" t="n">
-        <v>7429368</v>
+        <v>7429362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,10 +4178,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595613</v>
+        <v>122595636</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>97325</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4190,25 +4190,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4216,16 +4216,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800646</v>
+        <v>800929</v>
       </c>
       <c r="R35" t="n">
-        <v>7429350</v>
+        <v>7429308</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,6 +4270,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4284,10 +4289,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595595</v>
+        <v>122595900</v>
       </c>
       <c r="B36" t="n">
-        <v>98357</v>
+        <v>79384</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4296,25 +4301,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4328,10 +4333,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800518</v>
+        <v>800793</v>
       </c>
       <c r="R36" t="n">
-        <v>7429600</v>
+        <v>7429346</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4358,12 +4363,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4390,10 +4395,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595905</v>
+        <v>122595899</v>
       </c>
       <c r="B37" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4406,21 +4411,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4434,10 +4439,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800662</v>
+        <v>800751</v>
       </c>
       <c r="R37" t="n">
-        <v>7429278</v>
+        <v>7429412</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4496,10 +4501,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595921</v>
+        <v>122595914</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4512,21 +4517,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4540,10 +4545,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800444</v>
+        <v>800417</v>
       </c>
       <c r="R38" t="n">
-        <v>7429388</v>
+        <v>7429377</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4602,10 +4607,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595914</v>
+        <v>122595605</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4614,25 +4619,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4646,10 +4651,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800417</v>
+        <v>800481</v>
       </c>
       <c r="R39" t="n">
-        <v>7429377</v>
+        <v>7429318</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,12 +4681,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4708,10 +4713,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595906</v>
+        <v>122595614</v>
       </c>
       <c r="B40" t="n">
-        <v>79751</v>
+        <v>98365</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4720,25 +4725,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4752,10 +4757,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800557</v>
+        <v>800650</v>
       </c>
       <c r="R40" t="n">
-        <v>7429273</v>
+        <v>7429351</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,12 +4787,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4814,10 +4819,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595598</v>
+        <v>122595595</v>
       </c>
       <c r="B41" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4858,10 +4863,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800643</v>
+        <v>800518</v>
       </c>
       <c r="R41" t="n">
-        <v>7429444</v>
+        <v>7429600</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4920,10 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122595623</v>
+        <v>122595603</v>
       </c>
       <c r="B42" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4964,7 +4969,7 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>800714</v>
+        <v>800492</v>
       </c>
       <c r="R42" t="n">
         <v>7429368</v>
@@ -5026,10 +5031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595627</v>
+        <v>122595901</v>
       </c>
       <c r="B43" t="n">
-        <v>98357</v>
+        <v>78411</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5038,25 +5043,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5070,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800851</v>
+        <v>800786</v>
       </c>
       <c r="R43" t="n">
-        <v>7429442</v>
+        <v>7429304</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5100,12 +5105,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5132,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595596</v>
+        <v>122595898</v>
       </c>
       <c r="B44" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5144,25 +5149,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5176,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800535</v>
+        <v>800726</v>
       </c>
       <c r="R44" t="n">
-        <v>7429581</v>
+        <v>7429460</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5206,12 +5211,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5238,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595615</v>
+        <v>122595911</v>
       </c>
       <c r="B45" t="n">
-        <v>98357</v>
+        <v>94390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5250,25 +5255,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>2387</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5282,10 +5287,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800705</v>
+        <v>800419</v>
       </c>
       <c r="R45" t="n">
-        <v>7429329</v>
+        <v>7429341</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5312,12 +5317,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5344,10 +5349,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595604</v>
+        <v>122595607</v>
       </c>
       <c r="B46" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800482</v>
+        <v>800565</v>
       </c>
       <c r="R46" t="n">
-        <v>7429353</v>
+        <v>7429285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5450,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595618</v>
+        <v>122595596</v>
       </c>
       <c r="B47" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5494,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800702</v>
+        <v>800535</v>
       </c>
       <c r="R47" t="n">
-        <v>7429367</v>
+        <v>7429581</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5556,10 +5561,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595601</v>
+        <v>122595617</v>
       </c>
       <c r="B48" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5600,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800590</v>
+        <v>800705</v>
       </c>
       <c r="R48" t="n">
-        <v>7429490</v>
+        <v>7429310</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595590</v>
+        <v>122595612</v>
       </c>
       <c r="B49" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5706,10 +5711,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800672</v>
+        <v>800658</v>
       </c>
       <c r="R49" t="n">
-        <v>7429603</v>
+        <v>7429352</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5768,10 +5773,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595612</v>
+        <v>122595597</v>
       </c>
       <c r="B50" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5812,10 +5817,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800658</v>
+        <v>800611</v>
       </c>
       <c r="R50" t="n">
-        <v>7429352</v>
+        <v>7429547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5874,10 +5879,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595621</v>
+        <v>122595639</v>
       </c>
       <c r="B51" t="n">
-        <v>98357</v>
+        <v>92221</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5890,21 +5895,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>149</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5918,10 +5923,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800914</v>
+        <v>800773</v>
       </c>
       <c r="R51" t="n">
-        <v>7429341</v>
+        <v>7429354</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5980,10 +5985,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595629</v>
+        <v>122595915</v>
       </c>
       <c r="B52" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5992,25 +5997,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6024,10 +6029,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800859</v>
+        <v>800419</v>
       </c>
       <c r="R52" t="n">
-        <v>7429527</v>
+        <v>7429379</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6059,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,10 +6091,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595624</v>
+        <v>122595598</v>
       </c>
       <c r="B53" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800706</v>
+        <v>800643</v>
       </c>
       <c r="R53" t="n">
-        <v>7429365</v>
+        <v>7429444</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6192,10 +6197,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595614</v>
+        <v>122595620</v>
       </c>
       <c r="B54" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6236,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800650</v>
+        <v>800882</v>
       </c>
       <c r="R54" t="n">
-        <v>7429351</v>
+        <v>7429337</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6298,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595609</v>
+        <v>122595624</v>
       </c>
       <c r="B55" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6342,10 +6347,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800532</v>
+        <v>800706</v>
       </c>
       <c r="R55" t="n">
-        <v>7429301</v>
+        <v>7429365</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,10 +6409,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595606</v>
+        <v>122595621</v>
       </c>
       <c r="B56" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800535</v>
+        <v>800914</v>
       </c>
       <c r="R56" t="n">
-        <v>7429362</v>
+        <v>7429341</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6510,10 +6515,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595605</v>
+        <v>122595592</v>
       </c>
       <c r="B57" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6554,10 +6559,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800481</v>
+        <v>800614</v>
       </c>
       <c r="R57" t="n">
-        <v>7429318</v>
+        <v>7429556</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6616,10 +6621,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595622</v>
+        <v>122595921</v>
       </c>
       <c r="B58" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6628,25 +6633,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6660,10 +6665,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800857</v>
+        <v>800444</v>
       </c>
       <c r="R58" t="n">
-        <v>7429342</v>
+        <v>7429388</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6690,12 +6695,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6722,10 +6727,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595591</v>
+        <v>122595602</v>
       </c>
       <c r="B59" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6766,10 +6771,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800604</v>
+        <v>800439</v>
       </c>
       <c r="R59" t="n">
-        <v>7429623</v>
+        <v>7429345</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6828,10 +6833,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595593</v>
+        <v>122595629</v>
       </c>
       <c r="B60" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6872,10 +6877,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800567</v>
+        <v>800859</v>
       </c>
       <c r="R60" t="n">
-        <v>7429589</v>
+        <v>7429527</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6934,10 +6939,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595610</v>
+        <v>122595910</v>
       </c>
       <c r="B61" t="n">
-        <v>98357</v>
+        <v>79751</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6946,25 +6951,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6978,10 +6983,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800519</v>
+        <v>800412</v>
       </c>
       <c r="R61" t="n">
-        <v>7429306</v>
+        <v>7429327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7008,12 +7013,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595632</v>
+        <v>122595906</v>
       </c>
       <c r="B62" t="n">
-        <v>98357</v>
+        <v>79751</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7052,25 +7057,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7084,10 +7089,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800635</v>
+        <v>800557</v>
       </c>
       <c r="R62" t="n">
-        <v>7429538</v>
+        <v>7429273</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7114,12 +7119,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7146,10 +7151,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595611</v>
+        <v>122595905</v>
       </c>
       <c r="B63" t="n">
-        <v>98357</v>
+        <v>79384</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7158,25 +7163,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7190,10 +7195,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800599</v>
+        <v>800662</v>
       </c>
       <c r="R63" t="n">
-        <v>7429383</v>
+        <v>7429278</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7220,12 +7225,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7252,10 +7257,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595916</v>
+        <v>122595594</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7264,25 +7269,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -7296,10 +7301,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800420</v>
+        <v>800577</v>
       </c>
       <c r="R64" t="n">
-        <v>7429384</v>
+        <v>7429596</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7326,12 +7331,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7358,10 +7363,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595913</v>
+        <v>122595622</v>
       </c>
       <c r="B65" t="n">
-        <v>79751</v>
+        <v>98365</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7370,25 +7375,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7402,10 +7407,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800413</v>
+        <v>800857</v>
       </c>
       <c r="R65" t="n">
-        <v>7429375</v>
+        <v>7429342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7432,12 +7437,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7464,10 +7469,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595636</v>
+        <v>122595591</v>
       </c>
       <c r="B66" t="n">
-        <v>97317</v>
+        <v>98365</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7476,25 +7481,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7502,20 +7507,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800929</v>
+        <v>800604</v>
       </c>
       <c r="R66" t="n">
-        <v>7429308</v>
+        <v>7429623</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7556,7 +7557,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7575,10 +7575,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595911</v>
+        <v>122595609</v>
       </c>
       <c r="B67" t="n">
-        <v>94382</v>
+        <v>98365</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7587,25 +7587,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -7619,10 +7619,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800419</v>
+        <v>800532</v>
       </c>
       <c r="R67" t="n">
-        <v>7429341</v>
+        <v>7429301</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7649,12 +7649,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595638</v>
+        <v>122595640</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800789</v>
+        <v>800769</v>
       </c>
       <c r="R5" t="n">
-        <v>7429366</v>
+        <v>7429437</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595593</v>
+        <v>122595638</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800567</v>
+        <v>800789</v>
       </c>
       <c r="R6" t="n">
-        <v>7429589</v>
+        <v>7429366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595640</v>
+        <v>122595593</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800769</v>
+        <v>800567</v>
       </c>
       <c r="R7" t="n">
-        <v>7429437</v>
+        <v>7429589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595902</v>
+        <v>122595636</v>
       </c>
       <c r="B33" t="n">
-        <v>78503</v>
+        <v>97325</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3978,25 +3978,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4004,16 +4004,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800768</v>
+        <v>800929</v>
       </c>
       <c r="R33" t="n">
-        <v>7429299</v>
+        <v>7429308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4040,12 +4044,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4054,6 +4058,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4072,10 +4077,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595606</v>
+        <v>122595902</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>78503</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4084,25 +4089,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4116,10 +4121,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800535</v>
+        <v>800768</v>
       </c>
       <c r="R34" t="n">
-        <v>7429362</v>
+        <v>7429299</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,12 +4151,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4178,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595636</v>
+        <v>122595606</v>
       </c>
       <c r="B35" t="n">
-        <v>97325</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4190,25 +4195,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4216,20 +4221,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>800929</v>
+        <v>800535</v>
       </c>
       <c r="R35" t="n">
-        <v>7429308</v>
+        <v>7429362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4270,7 +4271,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595898</v>
+        <v>122595911</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>94390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5149,25 +5149,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800726</v>
+        <v>800419</v>
       </c>
       <c r="R44" t="n">
-        <v>7429460</v>
+        <v>7429341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5243,10 +5243,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595911</v>
+        <v>122595607</v>
       </c>
       <c r="B45" t="n">
-        <v>94390</v>
+        <v>98365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,25 +5255,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5287,10 +5287,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800419</v>
+        <v>800565</v>
       </c>
       <c r="R45" t="n">
-        <v>7429341</v>
+        <v>7429285</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5317,12 +5317,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5349,7 +5349,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595607</v>
+        <v>122595596</v>
       </c>
       <c r="B46" t="n">
         <v>98365</v>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800565</v>
+        <v>800535</v>
       </c>
       <c r="R46" t="n">
-        <v>7429285</v>
+        <v>7429581</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,10 +5455,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595596</v>
+        <v>122595898</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5467,25 +5467,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800535</v>
+        <v>800726</v>
       </c>
       <c r="R47" t="n">
-        <v>7429581</v>
+        <v>7429460</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122595917</v>
+        <v>122595893</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>800422</v>
+        <v>800464</v>
       </c>
       <c r="R2" t="n">
-        <v>7429390</v>
+        <v>7429456</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,22 +769,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122595604</v>
+        <v>122595639</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>149</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>800482</v>
+        <v>800773</v>
       </c>
       <c r="R3" t="n">
-        <v>7429353</v>
+        <v>7429354</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122595618</v>
+        <v>122595901</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>800702</v>
+        <v>800786</v>
       </c>
       <c r="R4" t="n">
-        <v>7429367</v>
+        <v>7429304</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122595640</v>
+        <v>122595894</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800769</v>
+        <v>800482</v>
       </c>
       <c r="R5" t="n">
-        <v>7429437</v>
+        <v>7429480</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,22 +1072,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122595638</v>
+        <v>122595911</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2387</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>800789</v>
+        <v>800419</v>
       </c>
       <c r="R6" t="n">
-        <v>7429366</v>
+        <v>7429341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,44 +1173,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122595593</v>
+        <v>122595638</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800567</v>
+        <v>800789</v>
       </c>
       <c r="R7" t="n">
-        <v>7429589</v>
+        <v>7429366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122595610</v>
+        <v>122595895</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1355,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800519</v>
+        <v>800486</v>
       </c>
       <c r="R8" t="n">
-        <v>7429306</v>
+        <v>7429476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,12 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1410,44 +1375,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122595635</v>
+        <v>122595897</v>
       </c>
       <c r="B9" t="n">
-        <v>97325</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1455,20 +1415,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>800874</v>
+        <v>800590</v>
       </c>
       <c r="R9" t="n">
-        <v>7429248</v>
+        <v>7429518</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,12 +1451,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,7 +1465,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1521,44 +1476,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122595893</v>
+        <v>122595898</v>
       </c>
       <c r="B10" t="n">
-        <v>95911</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1572,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800464</v>
+        <v>800726</v>
       </c>
       <c r="R10" t="n">
-        <v>7429456</v>
+        <v>7429460</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,26 +1577,21 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122595897</v>
+        <v>122595919</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1678,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800590</v>
+        <v>800416</v>
       </c>
       <c r="R11" t="n">
-        <v>7429518</v>
+        <v>7429404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1733,44 +1678,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122595913</v>
+        <v>122595921</v>
       </c>
       <c r="B12" t="n">
-        <v>79751</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1784,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>800413</v>
+        <v>800444</v>
       </c>
       <c r="R12" t="n">
-        <v>7429375</v>
+        <v>7429388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,22 +1779,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122595623</v>
+        <v>122595922</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,21 +1797,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800714</v>
+        <v>800561</v>
       </c>
       <c r="R13" t="n">
-        <v>7429368</v>
+        <v>7429400</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1920,12 +1855,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1945,44 +1880,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122595599</v>
+        <v>122595900</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1996,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800643</v>
+        <v>800793</v>
       </c>
       <c r="R14" t="n">
-        <v>7429452</v>
+        <v>7429346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,12 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,44 +1981,39 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122595619</v>
+        <v>122595905</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2102,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800707</v>
+        <v>800662</v>
       </c>
       <c r="R15" t="n">
-        <v>7429357</v>
+        <v>7429278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,12 +2057,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2157,44 +2082,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122595615</v>
+        <v>122595906</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2208,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800705</v>
+        <v>800557</v>
       </c>
       <c r="R16" t="n">
-        <v>7429329</v>
+        <v>7429273</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,12 +2158,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,44 +2183,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122595632</v>
+        <v>122595910</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2314,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800635</v>
+        <v>800412</v>
       </c>
       <c r="R17" t="n">
-        <v>7429538</v>
+        <v>7429327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,12 +2259,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,44 +2284,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122595903</v>
+        <v>122595913</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2420,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>800756</v>
+        <v>800413</v>
       </c>
       <c r="R18" t="n">
-        <v>7429284</v>
+        <v>7429375</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2475,44 +2385,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122595627</v>
+        <v>122595907</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2526,10 +2431,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800851</v>
+        <v>800547</v>
       </c>
       <c r="R19" t="n">
-        <v>7429442</v>
+        <v>7429255</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2556,12 +2461,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,44 +2486,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122595628</v>
+        <v>122595912</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2632,10 +2532,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800709</v>
+        <v>800405</v>
       </c>
       <c r="R20" t="n">
-        <v>7429466</v>
+        <v>7429382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,12 +2562,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,44 +2587,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122595625</v>
+        <v>122595914</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2738,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800705</v>
+        <v>800417</v>
       </c>
       <c r="R21" t="n">
-        <v>7429366</v>
+        <v>7429377</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,12 +2663,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,44 +2688,39 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122595616</v>
+        <v>122595915</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2844,10 +2734,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800708</v>
+        <v>800419</v>
       </c>
       <c r="R22" t="n">
-        <v>7429313</v>
+        <v>7429379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,12 +2764,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,44 +2789,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122595611</v>
+        <v>122595916</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2950,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800599</v>
+        <v>800420</v>
       </c>
       <c r="R23" t="n">
-        <v>7429383</v>
+        <v>7429384</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,12 +2865,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3005,22 +2890,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122595916</v>
+        <v>122595917</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3056,10 +2936,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800420</v>
+        <v>800422</v>
       </c>
       <c r="R24" t="n">
-        <v>7429384</v>
+        <v>7429390</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,44 +2991,39 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122595634</v>
+        <v>122595920</v>
       </c>
       <c r="B25" t="n">
-        <v>98283</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>223591</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3162,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>800580</v>
+        <v>800416</v>
       </c>
       <c r="R25" t="n">
-        <v>7429643</v>
+        <v>7429407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,12 +3067,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3217,44 +3092,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122595630</v>
+        <v>122595918</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3268,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>800696</v>
+        <v>800414</v>
       </c>
       <c r="R26" t="n">
-        <v>7429504</v>
+        <v>7429397</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3298,12 +3168,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,44 +3193,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122595590</v>
+        <v>122595892</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3374,10 +3239,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>800672</v>
+        <v>800523</v>
       </c>
       <c r="R27" t="n">
-        <v>7429603</v>
+        <v>7429275</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,12 +3269,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3429,44 +3294,39 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122595608</v>
+        <v>122595896</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3480,10 +3340,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>800522</v>
+        <v>800484</v>
       </c>
       <c r="R28" t="n">
-        <v>7429299</v>
+        <v>7429487</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3510,12 +3370,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,22 +3395,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122595601</v>
+        <v>122595590</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3586,10 +3441,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>800590</v>
+        <v>800672</v>
       </c>
       <c r="R29" t="n">
-        <v>7429490</v>
+        <v>7429603</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3648,15 +3503,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122595600</v>
+        <v>122595591</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3692,10 +3542,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>800475</v>
+        <v>800604</v>
       </c>
       <c r="R30" t="n">
-        <v>7429573</v>
+        <v>7429623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3754,15 +3604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122595633</v>
+        <v>122595592</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,10 +3643,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>800657</v>
+        <v>800614</v>
       </c>
       <c r="R31" t="n">
-        <v>7429608</v>
+        <v>7429556</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,15 +3705,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122595613</v>
+        <v>122595593</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3904,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>800646</v>
+        <v>800567</v>
       </c>
       <c r="R32" t="n">
-        <v>7429350</v>
+        <v>7429589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3966,37 +3806,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122595636</v>
+        <v>122595594</v>
       </c>
       <c r="B33" t="n">
-        <v>97325</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4004,20 +3839,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nordlandet, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>800929</v>
+        <v>800577</v>
       </c>
       <c r="R33" t="n">
-        <v>7429308</v>
+        <v>7429596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4058,7 +3889,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4077,37 +3907,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122595902</v>
+        <v>122595595</v>
       </c>
       <c r="B34" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4121,10 +3946,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>800768</v>
+        <v>800518</v>
       </c>
       <c r="R34" t="n">
-        <v>7429299</v>
+        <v>7429600</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4151,12 +3976,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4183,15 +4008,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122595606</v>
+        <v>122595596</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4230,7 +4050,7 @@
         <v>800535</v>
       </c>
       <c r="R35" t="n">
-        <v>7429362</v>
+        <v>7429581</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4289,37 +4109,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122595900</v>
+        <v>122595597</v>
       </c>
       <c r="B36" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,10 +4148,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>800793</v>
+        <v>800611</v>
       </c>
       <c r="R36" t="n">
-        <v>7429346</v>
+        <v>7429547</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4363,12 +4178,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,37 +4210,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122595899</v>
+        <v>122595598</v>
       </c>
       <c r="B37" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4439,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>800751</v>
+        <v>800643</v>
       </c>
       <c r="R37" t="n">
-        <v>7429412</v>
+        <v>7429444</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4469,12 +4279,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4501,37 +4311,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122595914</v>
+        <v>122595599</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4545,10 +4350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>800417</v>
+        <v>800643</v>
       </c>
       <c r="R38" t="n">
-        <v>7429377</v>
+        <v>7429452</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,12 +4380,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4607,15 +4412,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122595605</v>
+        <v>122595600</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4651,10 +4451,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>800481</v>
+        <v>800475</v>
       </c>
       <c r="R39" t="n">
-        <v>7429318</v>
+        <v>7429573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4713,15 +4513,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122595614</v>
+        <v>122595601</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,10 +4552,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>800650</v>
+        <v>800590</v>
       </c>
       <c r="R40" t="n">
-        <v>7429351</v>
+        <v>7429490</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4819,15 +4614,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122595595</v>
+        <v>122595602</v>
       </c>
       <c r="B41" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4863,10 +4653,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>800518</v>
+        <v>800439</v>
       </c>
       <c r="R41" t="n">
-        <v>7429600</v>
+        <v>7429345</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4928,12 +4718,7 @@
         <v>122595603</v>
       </c>
       <c r="B42" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5031,37 +4816,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122595901</v>
+        <v>122595604</v>
       </c>
       <c r="B43" t="n">
-        <v>78411</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5075,10 +4855,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>800786</v>
+        <v>800482</v>
       </c>
       <c r="R43" t="n">
-        <v>7429304</v>
+        <v>7429353</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5105,12 +4885,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5137,37 +4917,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122595911</v>
+        <v>122595605</v>
       </c>
       <c r="B44" t="n">
-        <v>94390</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2387</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5181,10 +4956,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>800419</v>
+        <v>800481</v>
       </c>
       <c r="R44" t="n">
-        <v>7429341</v>
+        <v>7429318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,12 +4986,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5243,15 +5018,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122595607</v>
+        <v>122595606</v>
       </c>
       <c r="B45" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5287,10 +5057,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>800565</v>
+        <v>800535</v>
       </c>
       <c r="R45" t="n">
-        <v>7429285</v>
+        <v>7429362</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5349,15 +5119,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122595596</v>
+        <v>122595607</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5393,10 +5158,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>800535</v>
+        <v>800565</v>
       </c>
       <c r="R46" t="n">
-        <v>7429581</v>
+        <v>7429285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,37 +5220,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122595898</v>
+        <v>122595608</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5499,10 +5259,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>800726</v>
+        <v>800522</v>
       </c>
       <c r="R47" t="n">
-        <v>7429460</v>
+        <v>7429299</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5529,12 +5289,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5561,15 +5321,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122595617</v>
+        <v>122595609</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5605,10 +5360,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>800705</v>
+        <v>800532</v>
       </c>
       <c r="R48" t="n">
-        <v>7429310</v>
+        <v>7429301</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5667,15 +5422,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122595612</v>
+        <v>122595610</v>
       </c>
       <c r="B49" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5711,10 +5461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>800658</v>
+        <v>800519</v>
       </c>
       <c r="R49" t="n">
-        <v>7429352</v>
+        <v>7429306</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5773,15 +5523,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122595597</v>
+        <v>122595611</v>
       </c>
       <c r="B50" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,10 +5562,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>800611</v>
+        <v>800599</v>
       </c>
       <c r="R50" t="n">
-        <v>7429547</v>
+        <v>7429383</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5879,15 +5624,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122595639</v>
+        <v>122595612</v>
       </c>
       <c r="B51" t="n">
-        <v>92221</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5895,21 +5635,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>149</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5923,10 +5663,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>800773</v>
+        <v>800658</v>
       </c>
       <c r="R51" t="n">
-        <v>7429354</v>
+        <v>7429352</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5985,37 +5725,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122595915</v>
+        <v>122595613</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6029,10 +5764,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>800419</v>
+        <v>800646</v>
       </c>
       <c r="R52" t="n">
-        <v>7429379</v>
+        <v>7429350</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6059,12 +5794,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6091,15 +5826,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122595598</v>
+        <v>122595614</v>
       </c>
       <c r="B53" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6135,10 +5865,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>800643</v>
+        <v>800650</v>
       </c>
       <c r="R53" t="n">
-        <v>7429444</v>
+        <v>7429351</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6197,15 +5927,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122595620</v>
+        <v>122595615</v>
       </c>
       <c r="B54" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6241,10 +5966,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>800882</v>
+        <v>800705</v>
       </c>
       <c r="R54" t="n">
-        <v>7429337</v>
+        <v>7429329</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6303,15 +6028,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122595624</v>
+        <v>122595616</v>
       </c>
       <c r="B55" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6347,10 +6067,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>800706</v>
+        <v>800708</v>
       </c>
       <c r="R55" t="n">
-        <v>7429365</v>
+        <v>7429313</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6409,15 +6129,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122595621</v>
+        <v>122595617</v>
       </c>
       <c r="B56" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6453,10 +6168,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>800914</v>
+        <v>800705</v>
       </c>
       <c r="R56" t="n">
-        <v>7429341</v>
+        <v>7429310</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6515,15 +6230,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122595592</v>
+        <v>122595618</v>
       </c>
       <c r="B57" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6559,10 +6269,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>800614</v>
+        <v>800702</v>
       </c>
       <c r="R57" t="n">
-        <v>7429556</v>
+        <v>7429367</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6621,37 +6331,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122595921</v>
+        <v>122595619</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6665,10 +6370,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>800444</v>
+        <v>800707</v>
       </c>
       <c r="R58" t="n">
-        <v>7429388</v>
+        <v>7429357</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6695,12 +6400,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6727,15 +6432,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122595602</v>
+        <v>122595620</v>
       </c>
       <c r="B59" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6771,10 +6471,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>800439</v>
+        <v>800882</v>
       </c>
       <c r="R59" t="n">
-        <v>7429345</v>
+        <v>7429337</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6833,15 +6533,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122595629</v>
+        <v>122595621</v>
       </c>
       <c r="B60" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6877,10 +6572,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>800859</v>
+        <v>800914</v>
       </c>
       <c r="R60" t="n">
-        <v>7429527</v>
+        <v>7429341</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6939,37 +6634,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122595910</v>
+        <v>122595622</v>
       </c>
       <c r="B61" t="n">
-        <v>79751</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6983,10 +6673,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>800412</v>
+        <v>800857</v>
       </c>
       <c r="R61" t="n">
-        <v>7429327</v>
+        <v>7429342</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7013,12 +6703,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7045,37 +6735,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122595906</v>
+        <v>122595623</v>
       </c>
       <c r="B62" t="n">
-        <v>79751</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7089,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>800557</v>
+        <v>800714</v>
       </c>
       <c r="R62" t="n">
-        <v>7429273</v>
+        <v>7429368</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7119,12 +6804,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7151,37 +6836,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122595905</v>
+        <v>122595624</v>
       </c>
       <c r="B63" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -7195,10 +6875,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>800662</v>
+        <v>800706</v>
       </c>
       <c r="R63" t="n">
-        <v>7429278</v>
+        <v>7429365</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7225,12 +6905,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7257,15 +6937,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122595594</v>
+        <v>122595625</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7301,10 +6976,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>800577</v>
+        <v>800705</v>
       </c>
       <c r="R64" t="n">
-        <v>7429596</v>
+        <v>7429366</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7363,15 +7038,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122595622</v>
+        <v>122595627</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7407,10 +7077,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>800857</v>
+        <v>800851</v>
       </c>
       <c r="R65" t="n">
-        <v>7429342</v>
+        <v>7429442</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7469,15 +7139,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122595591</v>
+        <v>122595628</v>
       </c>
       <c r="B66" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7513,10 +7178,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>800604</v>
+        <v>800709</v>
       </c>
       <c r="R66" t="n">
-        <v>7429623</v>
+        <v>7429466</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7575,15 +7240,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122595609</v>
+        <v>122595629</v>
       </c>
       <c r="B67" t="n">
-        <v>98365</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7619,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>800532</v>
+        <v>800859</v>
       </c>
       <c r="R67" t="n">
-        <v>7429301</v>
+        <v>7429527</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7678,6 +7338,1228 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122595630</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>800696</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7429504</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>122595632</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>800635</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7429538</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122595633</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>800657</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7429608</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122595806</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>800603</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7429317</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122595635</v>
+      </c>
+      <c r="B72" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>800874</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7429248</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122595636</v>
+      </c>
+      <c r="B73" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>800929</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7429308</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122595923</v>
+      </c>
+      <c r="B74" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>800569</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7429388</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122595634</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>800580</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7429643</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122595640</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>800769</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7429437</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122595899</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>800751</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7429412</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122595902</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>800768</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7429299</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122595903</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Nordlandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>800756</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7429284</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23357-2024 artfynd.xlsx
+++ b/artfynd/A 23357-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595911</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595895</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595919</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595921</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595910</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595913</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595912</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595914</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595915</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595916</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595917</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595920</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595896</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595600</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595602</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595604</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595605</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595639</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595901</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595638</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595897</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595898</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595922</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595900</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3500,6 +3640,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595905</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3601,6 +3746,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595906</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3702,6 +3852,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595907</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3803,6 +3958,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595892</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3904,6 +4064,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595590</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4005,6 +4170,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595591</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4106,6 +4276,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595592</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4207,6 +4382,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595593</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4308,6 +4488,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595594</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4409,6 +4594,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595595</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4510,6 +4700,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595596</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4611,6 +4806,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595597</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4712,6 +4912,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595598</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4813,6 +5018,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595599</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4914,6 +5124,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595601</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5015,6 +5230,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595603</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5116,6 +5336,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595606</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5217,6 +5442,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595607</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5318,6 +5548,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595608</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5419,6 +5654,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595609</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5520,6 +5760,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595610</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5621,6 +5866,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595611</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5722,6 +5972,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595612</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5823,6 +6078,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595613</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5924,6 +6184,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595614</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6025,6 +6290,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595615</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6126,6 +6396,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595616</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6227,6 +6502,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595617</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6328,6 +6608,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595618</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6429,6 +6714,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595619</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6530,6 +6820,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595620</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6631,6 +6926,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595621</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6732,6 +7032,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595622</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6833,6 +7138,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595623</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6934,6 +7244,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595624</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7035,6 +7350,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595625</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7136,6 +7456,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595627</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7237,6 +7562,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595628</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7338,6 +7668,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595629</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7439,6 +7774,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595630</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7540,6 +7880,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595632</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7641,6 +7986,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595633</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7742,6 +8092,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595806</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7848,6 +8203,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595635</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7954,6 +8314,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595636</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8055,6 +8420,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595923</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8156,6 +8526,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595634</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8257,6 +8632,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595640</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8358,6 +8738,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595899</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8459,6 +8844,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595902</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8560,8 +8950,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122595903</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>